--- a/Collections/India/#Republic_of_India#Regular#[1957-present]#circulation_quality.xlsx
+++ b/Collections/India/#Republic_of_India#Regular#[1957-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\India\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21CB29A-402E-45A1-AF02-751A3AAA9FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C2A210-6696-48B2-B74D-FEA9AFF0B29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1 Paisa" sheetId="28" r:id="rId1"/>
@@ -53,6 +53,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2275,7 +2278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13363" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13894" uniqueCount="333">
   <si>
     <t>-</t>
   </si>
@@ -3551,7 +3554,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3645,6 +3648,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3706,15 +3712,6 @@
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="794">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -10043,6 +10040,15 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -10071,9 +10077,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="793"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="792" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="791"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -10376,7 +10382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -10389,28 +10395,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="32" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="35" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -13160,6 +13166,123 @@
       </c>
       <c r="L72" s="17" t="str">
         <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I73" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J73" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L73" s="17" t="str">
+        <f t="shared" ref="L73:L75" si="7">IF(OR(AND(I73&gt;1,I73&lt;&gt;"-"),AND(J73&gt;1,J73&lt;&gt;"-"),AND(K73&gt;1,K73&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I74" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J74" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L74" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I75" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J75" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L75" s="17" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -13184,7 +13307,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3 I5 I7 I9 I11 I19">
-    <cfRule type="containsText" dxfId="793" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="790" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13309,7 +13432,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3 J5 J7 J9 J11">
-    <cfRule type="containsText" dxfId="792" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="789" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13326,7 +13449,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3 K5 K7 K9 K11">
-    <cfRule type="containsText" dxfId="791" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="788" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13343,7 +13466,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4 I6 I8 I10 I21">
-    <cfRule type="containsText" dxfId="790" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="787" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13360,7 +13483,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6 J8 J10 J21">
-    <cfRule type="containsText" dxfId="789" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="786" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13377,7 +13500,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6 K8 K10">
-    <cfRule type="containsText" dxfId="788" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="785" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13394,7 +13517,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="787" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="784" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13411,52 +13534,52 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="786" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="783" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="785" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="782" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="784" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="781" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="783" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="780" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="782" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="779" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="781" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="778" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="780" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="777" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="779" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="776" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="778" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="775" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="777" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="774" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13473,7 +13596,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="containsText" dxfId="776" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="773" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13490,7 +13613,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="775" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="772" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13502,7 +13625,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8095C98-5C80-45BB-89F7-82C890B1C80E}">
-  <dimension ref="A1:W97"/>
+  <dimension ref="A1:W100"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -13517,39 +13640,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="44" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="48" t="s">
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="49" t="s">
         <v>290</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -20283,6 +20406,216 @@
       </c>
       <c r="W97" s="17" t="str">
         <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="M98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="N98" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="O98" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P98" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R98" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="S98" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="T98" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="U98" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="V98" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="W98" s="17" t="str">
+        <f t="shared" ref="W98:W100" si="7">IF(OR(AND(O98&gt;1,O98&lt;&gt;"-"),AND(P98&gt;1,P98&lt;&gt;"-"),AND(R98&gt;1,R98&lt;&gt;"-"),AND(S98&gt;1,S98&lt;&gt;"-"),AND(T98&gt;1,T98&lt;&gt;"-"),AND(U98&gt;1,U98&lt;&gt;"-"),AND(V98&gt;1,V98&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="M99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="N99" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="O99" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P99" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R99" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="S99" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="T99" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="U99" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="V99" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="W99" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="M100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="N100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="O100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="S100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="T100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="U100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="V100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="W100" s="17" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -20427,7 +20760,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P38">
-    <cfRule type="containsText" dxfId="247" priority="343" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="244" priority="343" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20444,7 +20777,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q38:Q39">
-    <cfRule type="containsText" dxfId="246" priority="341" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="243" priority="341" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20557,7 +20890,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P29">
-    <cfRule type="containsText" dxfId="245" priority="347" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="242" priority="347" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20574,7 +20907,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q29">
-    <cfRule type="containsText" dxfId="244" priority="345" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="241" priority="345" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20591,7 +20924,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P46">
-    <cfRule type="containsText" dxfId="243" priority="309" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="240" priority="309" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20608,7 +20941,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q46">
-    <cfRule type="containsText" dxfId="242" priority="307" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="239" priority="307" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20625,7 +20958,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O38">
-    <cfRule type="containsText" dxfId="241" priority="339" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="238" priority="339" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20642,7 +20975,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O40">
-    <cfRule type="containsText" dxfId="240" priority="337" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="237" priority="337" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20659,7 +20992,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42 P54 P69 P72">
-    <cfRule type="containsText" dxfId="239" priority="335" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="236" priority="335" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20676,7 +21009,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q42 Q45 Q50 Q64 Q69 Q72">
-    <cfRule type="containsText" dxfId="238" priority="333" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="235" priority="333" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20693,7 +21026,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O42 O45 O50 O69 O72">
-    <cfRule type="containsText" dxfId="237" priority="331" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="234" priority="331" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20710,7 +21043,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P44 P47 P67">
-    <cfRule type="containsText" dxfId="236" priority="329" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="233" priority="329" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20727,7 +21060,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44 Q53 Q67 Q70 Q47">
-    <cfRule type="containsText" dxfId="235" priority="327" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="232" priority="327" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20744,7 +21077,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O44 O47 O53">
-    <cfRule type="containsText" dxfId="234" priority="325" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="231" priority="325" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20785,17 +21118,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P43">
-    <cfRule type="containsText" dxfId="233" priority="323" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="230" priority="323" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="containsText" dxfId="232" priority="313" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="229" priority="313" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R51">
-    <cfRule type="containsText" dxfId="231" priority="277" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="228" priority="277" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20812,7 +21145,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R46">
-    <cfRule type="containsText" dxfId="230" priority="303" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="227" priority="303" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20829,7 +21162,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R42 R45 R69">
-    <cfRule type="containsText" dxfId="229" priority="315" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="226" priority="315" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20846,7 +21179,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R48">
-    <cfRule type="containsText" dxfId="228" priority="295" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="225" priority="295" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20863,7 +21196,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S58">
-    <cfRule type="containsText" dxfId="227" priority="221" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="224" priority="221" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20904,17 +21237,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P76">
-    <cfRule type="containsText" dxfId="226" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="223" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O62">
-    <cfRule type="containsText" dxfId="225" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="222" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O46">
-    <cfRule type="containsText" dxfId="224" priority="305" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="221" priority="305" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20931,7 +21264,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q60">
-    <cfRule type="containsText" dxfId="223" priority="203" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="220" priority="203" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20984,22 +21317,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P48">
-    <cfRule type="containsText" dxfId="222" priority="301" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="219" priority="301" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R58">
-    <cfRule type="containsText" dxfId="221" priority="235" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="218" priority="235" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O48">
-    <cfRule type="containsText" dxfId="220" priority="297" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="217" priority="297" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O51">
-    <cfRule type="containsText" dxfId="219" priority="279" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="216" priority="279" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21052,22 +21385,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P52">
-    <cfRule type="containsText" dxfId="218" priority="275" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="215" priority="275" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R62">
-    <cfRule type="containsText" dxfId="217" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="214" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O52">
-    <cfRule type="containsText" dxfId="216" priority="271" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="213" priority="271" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T62">
-    <cfRule type="containsText" dxfId="215" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="212" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21084,7 +21417,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P49">
-    <cfRule type="containsText" dxfId="214" priority="285" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="211" priority="285" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21137,17 +21470,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P51">
-    <cfRule type="containsText" dxfId="213" priority="283" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="210" priority="283" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O55">
-    <cfRule type="containsText" dxfId="212" priority="263" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="209" priority="263" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65">
-    <cfRule type="containsText" dxfId="211" priority="185" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="208" priority="185" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21200,22 +21533,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P68">
-    <cfRule type="containsText" dxfId="210" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="207" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R65">
-    <cfRule type="containsText" dxfId="209" priority="181" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="206" priority="181" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R61">
-    <cfRule type="containsText" dxfId="208" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="205" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V65">
-    <cfRule type="containsText" dxfId="207" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="204" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21268,22 +21601,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P55">
-    <cfRule type="containsText" dxfId="206" priority="267" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="203" priority="267" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80">
-    <cfRule type="containsText" dxfId="205" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="202" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64">
-    <cfRule type="containsText" dxfId="204" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="201" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q79">
-    <cfRule type="containsText" dxfId="203" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="200" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21336,17 +21669,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q56">
-    <cfRule type="containsText" dxfId="202" priority="257" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="199" priority="257" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O71">
-    <cfRule type="containsText" dxfId="201" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="198" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U58">
-    <cfRule type="containsText" dxfId="200" priority="223" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="197" priority="223" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21363,7 +21696,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S55">
-    <cfRule type="containsText" dxfId="199" priority="251" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="196" priority="251" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21404,7 +21737,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O80">
-    <cfRule type="containsText" dxfId="198" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="195" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21421,32 +21754,32 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R57">
-    <cfRule type="containsText" dxfId="197" priority="243" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="194" priority="243" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P59">
-    <cfRule type="containsText" dxfId="196" priority="225" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="193" priority="225" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R81">
-    <cfRule type="containsText" dxfId="195" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="192" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R68">
-    <cfRule type="containsText" dxfId="194" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="191" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q74">
-    <cfRule type="containsText" dxfId="193" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="190" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q82">
-    <cfRule type="containsText" dxfId="192" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="189" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21487,22 +21820,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O58">
-    <cfRule type="containsText" dxfId="191" priority="237" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="188" priority="237" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O79">
-    <cfRule type="containsText" dxfId="190" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="187" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P58">
-    <cfRule type="containsText" dxfId="189" priority="241" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="186" priority="241" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O65">
-    <cfRule type="containsText" dxfId="188" priority="183" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="185" priority="183" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21543,22 +21876,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q78">
-    <cfRule type="containsText" dxfId="187" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="184" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R84">
-    <cfRule type="containsText" dxfId="186" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="183" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P79">
-    <cfRule type="containsText" dxfId="185" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="182" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="containsText" dxfId="184" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="181" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21575,12 +21908,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80">
-    <cfRule type="containsText" dxfId="183" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="180" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q63">
-    <cfRule type="containsText" dxfId="182" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="179" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21597,7 +21930,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P86 P88 P90 P92">
-    <cfRule type="containsText" dxfId="181" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="178" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21638,17 +21971,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q85 Q87 Q89 Q91 Q93">
-    <cfRule type="containsText" dxfId="180" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="177" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O85 O87 O89 O91 O93">
-    <cfRule type="containsText" dxfId="179" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="176" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q62">
-    <cfRule type="containsText" dxfId="178" priority="199" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="175" priority="199" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21689,17 +22022,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80">
-    <cfRule type="containsText" dxfId="177" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="174" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R78">
-    <cfRule type="containsText" dxfId="176" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="173" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O68">
-    <cfRule type="containsText" dxfId="175" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="172" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21728,22 +22061,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q71">
-    <cfRule type="containsText" dxfId="174" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="171" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q75">
-    <cfRule type="containsText" dxfId="173" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="170" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O78">
-    <cfRule type="containsText" dxfId="172" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="169" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P62">
-    <cfRule type="containsText" dxfId="171" priority="201" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="168" priority="201" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21760,12 +22093,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q81">
-    <cfRule type="containsText" dxfId="170" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="167" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q73">
-    <cfRule type="containsText" dxfId="169" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="166" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21794,17 +22127,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P65">
-    <cfRule type="containsText" dxfId="168" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="165" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O82">
-    <cfRule type="containsText" dxfId="167" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="164" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R82">
-    <cfRule type="containsText" dxfId="166" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="163" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21845,22 +22178,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O75">
-    <cfRule type="containsText" dxfId="165" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="162" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q84">
-    <cfRule type="containsText" dxfId="164" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="161" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O86 O88 O90 O92">
-    <cfRule type="containsText" dxfId="163" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="160" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q66">
-    <cfRule type="containsText" dxfId="162" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="159" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21889,27 +22222,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O84">
-    <cfRule type="containsText" dxfId="161" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="158" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P71">
-    <cfRule type="containsText" dxfId="160" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="157" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O81">
-    <cfRule type="containsText" dxfId="159" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="156" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R71">
-    <cfRule type="containsText" dxfId="158" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="155" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P82">
-    <cfRule type="containsText" dxfId="157" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="154" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21938,22 +22271,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O83">
-    <cfRule type="containsText" dxfId="156" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="153" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R86 R88 R90">
-    <cfRule type="containsText" dxfId="155" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="152" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R85 R87 R89 R91 R93">
-    <cfRule type="containsText" dxfId="154" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="151" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83">
-    <cfRule type="containsText" dxfId="153" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="150" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21970,27 +22303,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P85 P87 P89 P91 P93">
-    <cfRule type="containsText" dxfId="152" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="149" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83">
-    <cfRule type="containsText" dxfId="151" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="148" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q86 Q88 Q90 Q92">
-    <cfRule type="containsText" dxfId="150" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="147" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P77">
-    <cfRule type="containsText" dxfId="149" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="146" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P81">
-    <cfRule type="containsText" dxfId="148" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="145" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22007,7 +22340,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O94">
-    <cfRule type="containsText" dxfId="147" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="144" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22036,12 +22369,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R94">
-    <cfRule type="containsText" dxfId="146" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="143" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P94">
-    <cfRule type="containsText" dxfId="145" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="142" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22058,12 +22391,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q96">
-    <cfRule type="containsText" dxfId="144" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="141" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O96">
-    <cfRule type="containsText" dxfId="143" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="140" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22104,12 +22437,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R96">
-    <cfRule type="containsText" dxfId="142" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="139" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P96">
-    <cfRule type="containsText" dxfId="141" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="138" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22126,7 +22459,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O95">
-    <cfRule type="containsText" dxfId="140" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="137" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22155,12 +22488,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R95">
-    <cfRule type="containsText" dxfId="139" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="136" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P95">
-    <cfRule type="containsText" dxfId="138" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="135" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22172,7 +22505,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A0D83EC-774C-4596-9CBC-88ABC532501C}">
-  <dimension ref="A1:P94"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -22186,32 +22519,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="44" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="48" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -26849,7 +27182,7 @@
         <v>0</v>
       </c>
       <c r="P93" s="17" t="str">
-        <f t="shared" ref="P93:P94" si="5">IF(OR(AND(K93&gt;1,K93&lt;&gt;"-"),AND(L93&gt;1,L93&lt;&gt;"-"),AND(M93&gt;1,M93&lt;&gt;"-"),AND(N93&gt;1,N93&lt;&gt;"-"),AND(O93&gt;1,O93&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="P93:P97" si="5">IF(OR(AND(K93&gt;1,K93&lt;&gt;"-"),AND(L93&gt;1,L93&lt;&gt;"-"),AND(M93&gt;1,M93&lt;&gt;"-"),AND(N93&gt;1,N93&lt;&gt;"-"),AND(O93&gt;1,O93&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -26898,6 +27231,159 @@
         <v>0</v>
       </c>
       <c r="P94" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F95" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G95" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H95" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I95" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J95" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K95" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L95" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M95" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N95" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O95" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P95" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F96" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G96" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H96" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I96" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J96" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K96" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L96" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M96" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N96" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O96" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P96" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F97" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G97" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H97" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I97" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J97" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K97" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L97" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M97" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N97" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O97" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P97" s="17" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -27103,7 +27589,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63">
-    <cfRule type="containsText" dxfId="137" priority="223" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="134" priority="223" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27120,56 +27606,56 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L63">
-    <cfRule type="containsText" dxfId="136" priority="221" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="133" priority="221" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L38 L42 L46 L50 L55">
-    <cfRule type="containsText" dxfId="135" priority="309" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="132" priority="309" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M38 M42 M46 M50 M55">
-    <cfRule type="containsText" dxfId="134" priority="307" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="131" priority="307" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M63">
-    <cfRule type="containsText" dxfId="133" priority="219" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="130" priority="219" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N45">
-    <cfRule type="containsText" dxfId="132" priority="217" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="129" priority="217" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47">
-    <cfRule type="containsText" dxfId="131" priority="215" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="128" priority="215" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38 K42 K46 K50 K55">
-    <cfRule type="containsText" dxfId="130" priority="311" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="127" priority="311" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47">
-    <cfRule type="containsText" dxfId="129" priority="211" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="126" priority="211" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47">
-    <cfRule type="containsText" dxfId="128" priority="209" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="125" priority="209" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L47">
-    <cfRule type="containsText" dxfId="127" priority="213" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="124" priority="213" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L44 L40 L52">
+  <conditionalFormatting sqref="L40 L44 L52">
     <cfRule type="colorScale" priority="304">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27182,11 +27668,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40 L44 L52">
-    <cfRule type="containsText" dxfId="126" priority="303" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="123" priority="303" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K44 K40 K52 K57">
+  <conditionalFormatting sqref="K40 K44 K52 K57">
     <cfRule type="colorScale" priority="306">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27199,7 +27685,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40 K44 K52 K57">
-    <cfRule type="containsText" dxfId="125" priority="305" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="122" priority="305" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27240,17 +27726,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49">
-    <cfRule type="containsText" dxfId="124" priority="207" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="121" priority="207" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49">
-    <cfRule type="containsText" dxfId="123" priority="205" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="120" priority="205" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M44 M52 M57 M61">
-    <cfRule type="containsText" dxfId="122" priority="301" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="119" priority="301" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27291,17 +27777,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K48">
-    <cfRule type="containsText" dxfId="121" priority="299" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="118" priority="299" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L48">
-    <cfRule type="containsText" dxfId="120" priority="297" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="117" priority="297" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49">
-    <cfRule type="containsText" dxfId="119" priority="203" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="116" priority="203" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27330,12 +27816,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N49">
-    <cfRule type="containsText" dxfId="118" priority="201" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="115" priority="201" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K51">
-    <cfRule type="containsText" dxfId="117" priority="199" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="114" priority="199" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27352,7 +27838,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50">
-    <cfRule type="containsText" dxfId="116" priority="295" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="113" priority="295" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27369,7 +27855,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K59">
-    <cfRule type="containsText" dxfId="115" priority="293" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="112" priority="293" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27386,7 +27872,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59">
-    <cfRule type="containsText" dxfId="114" priority="291" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="111" priority="291" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27427,17 +27913,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L39">
-    <cfRule type="containsText" dxfId="113" priority="287" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="110" priority="287" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M39">
-    <cfRule type="containsText" dxfId="112" priority="285" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="109" priority="285" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="containsText" dxfId="111" priority="289" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="108" priority="289" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27478,17 +27964,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L41">
-    <cfRule type="containsText" dxfId="110" priority="281" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="107" priority="281" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M41">
-    <cfRule type="containsText" dxfId="109" priority="279" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="106" priority="279" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="containsText" dxfId="108" priority="283" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="105" priority="283" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27529,17 +28015,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L43">
-    <cfRule type="containsText" dxfId="107" priority="275" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="104" priority="275" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M43">
-    <cfRule type="containsText" dxfId="106" priority="273" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="103" priority="273" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="containsText" dxfId="105" priority="277" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="102" priority="277" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27580,17 +28066,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="containsText" dxfId="104" priority="269" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="101" priority="269" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M45">
-    <cfRule type="containsText" dxfId="103" priority="267" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="100" priority="267" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K45">
-    <cfRule type="containsText" dxfId="102" priority="271" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="99" priority="271" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27631,17 +28117,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60">
-    <cfRule type="containsText" dxfId="101" priority="225" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="98" priority="225" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N53">
-    <cfRule type="containsText" dxfId="100" priority="185" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="97" priority="185" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L60">
-    <cfRule type="containsText" dxfId="99" priority="227" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="96" priority="227" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27682,17 +28168,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58">
-    <cfRule type="containsText" dxfId="98" priority="235" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="95" priority="235" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L58">
-    <cfRule type="containsText" dxfId="97" priority="233" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="94" priority="233" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M53">
-    <cfRule type="containsText" dxfId="96" priority="243" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="93" priority="243" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27733,17 +28219,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K56">
-    <cfRule type="containsText" dxfId="95" priority="181" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="92" priority="181" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L56">
-    <cfRule type="containsText" dxfId="94" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="91" priority="179" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L53">
-    <cfRule type="containsText" dxfId="93" priority="245" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="90" priority="245" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27784,17 +28270,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O53">
-    <cfRule type="containsText" dxfId="92" priority="183" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="89" priority="183" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L68">
-    <cfRule type="containsText" dxfId="91" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="88" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K53">
-    <cfRule type="containsText" dxfId="90" priority="247" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="87" priority="247" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27835,17 +28321,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M56">
-    <cfRule type="containsText" dxfId="89" priority="177" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="86" priority="177" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M58">
-    <cfRule type="containsText" dxfId="88" priority="231" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="85" priority="231" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M68">
-    <cfRule type="containsText" dxfId="87" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="84" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27886,17 +28372,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="containsText" dxfId="86" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="83" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N56">
-    <cfRule type="containsText" dxfId="85" priority="175" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="82" priority="175" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K75">
-    <cfRule type="containsText" dxfId="84" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="81" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27937,17 +28423,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67">
-    <cfRule type="containsText" dxfId="83" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="80" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67">
-    <cfRule type="containsText" dxfId="82" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="79" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M66">
-    <cfRule type="containsText" dxfId="81" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27988,17 +28474,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L51">
-    <cfRule type="containsText" dxfId="80" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M51">
-    <cfRule type="containsText" dxfId="79" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M67">
-    <cfRule type="containsText" dxfId="78" priority="149" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="75" priority="149" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28015,7 +28501,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N51">
-    <cfRule type="containsText" dxfId="77" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="74" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28056,17 +28542,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M69">
-    <cfRule type="containsText" dxfId="76" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="73" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L77">
-    <cfRule type="containsText" dxfId="75" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="72" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K68">
-    <cfRule type="containsText" dxfId="74" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28083,7 +28569,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N62">
-    <cfRule type="containsText" dxfId="73" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="70" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28112,12 +28598,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M75">
-    <cfRule type="containsText" dxfId="72" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K71">
-    <cfRule type="containsText" dxfId="71" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="68" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28134,11 +28620,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L76">
-    <cfRule type="containsText" dxfId="70" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M84 M80 M86 M89">
+  <conditionalFormatting sqref="M80 M84 M86 M89">
     <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28175,17 +28661,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O56">
-    <cfRule type="containsText" dxfId="69" priority="173" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="173" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M80 M84 M86 M89">
-    <cfRule type="containsText" dxfId="68" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K73">
-    <cfRule type="containsText" dxfId="67" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="64" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28202,7 +28688,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N80 N84 N86 N89">
-    <cfRule type="containsText" dxfId="66" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="63" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28219,17 +28705,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N60">
-    <cfRule type="containsText" dxfId="65" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="62" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N58">
-    <cfRule type="containsText" dxfId="64" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="61" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L74">
-    <cfRule type="containsText" dxfId="63" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28246,12 +28732,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N75">
-    <cfRule type="containsText" dxfId="62" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="59" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M79">
-    <cfRule type="containsText" dxfId="61" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="58" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28268,7 +28754,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M62">
-    <cfRule type="containsText" dxfId="60" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="57" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28285,11 +28771,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L62">
-    <cfRule type="containsText" dxfId="59" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K82 K78 K85 K87 K90">
+  <conditionalFormatting sqref="K78 K82 K85 K87 K90">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28302,7 +28788,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K62">
-    <cfRule type="containsText" dxfId="58" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="55" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28318,7 +28804,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N82 N78 N85 N87 N90">
+  <conditionalFormatting sqref="N78 N82 N85 N87 N90">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28330,7 +28816,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M82 M78 M85 M87">
+  <conditionalFormatting sqref="M78 M82 M85 M87">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28343,16 +28829,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L80 L84 L86 L89">
-    <cfRule type="containsText" dxfId="57" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="54" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78 K82 K85 K87 K90">
-    <cfRule type="containsText" dxfId="56" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="53" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L82 L78 L85 L87 L90">
+  <conditionalFormatting sqref="L78 L82 L85 L87 L90">
     <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28365,12 +28851,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M78 M82 M85 M87">
-    <cfRule type="containsText" dxfId="55" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="52" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N78 N82 N85 N87 N90">
-    <cfRule type="containsText" dxfId="54" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28387,11 +28873,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M70">
-    <cfRule type="containsText" dxfId="53" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="50" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K84 K80 K86 K89">
+  <conditionalFormatting sqref="K80 K84 K86 K89">
     <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28404,12 +28890,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M81">
-    <cfRule type="containsText" dxfId="52" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K72">
-    <cfRule type="containsText" dxfId="51" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28426,12 +28912,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80 K84 K86 K89">
-    <cfRule type="containsText" dxfId="50" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L78 L82 L85 L87 L90">
-    <cfRule type="containsText" dxfId="49" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28472,22 +28958,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M88">
-    <cfRule type="containsText" dxfId="48" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N93">
-    <cfRule type="containsText" dxfId="47" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="44" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K92">
-    <cfRule type="containsText" dxfId="46" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83">
-    <cfRule type="containsText" dxfId="45" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28504,7 +28990,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M92">
-    <cfRule type="containsText" dxfId="44" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="41" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28521,7 +29007,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L92">
-    <cfRule type="containsText" dxfId="43" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28538,7 +29024,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93">
-    <cfRule type="containsText" dxfId="42" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28555,12 +29041,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N92">
-    <cfRule type="containsText" dxfId="41" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N88">
-    <cfRule type="containsText" dxfId="40" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28577,7 +29063,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L93">
-    <cfRule type="containsText" dxfId="39" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28606,7 +29092,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L94">
-    <cfRule type="containsText" dxfId="38" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28623,7 +29109,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K91">
-    <cfRule type="containsText" dxfId="37" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28640,7 +29126,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L91">
-    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28657,7 +29143,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M93">
-    <cfRule type="containsText" dxfId="35" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28674,12 +29160,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M94">
-    <cfRule type="containsText" dxfId="34" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N91">
-    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28708,7 +29194,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M91">
-    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28720,7 +29206,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D658D4-3176-4DBB-B862-72BFB0FE53E0}">
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -28733,30 +29219,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="44" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="48" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49" t="s">
         <v>322</v>
       </c>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="51"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -31638,7 +32124,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="17" t="str">
-        <f t="shared" ref="N66:N69" si="8">IF(OR(AND(J66&gt;1,J66&lt;&gt;"-"),AND(K66&gt;1,K66&lt;&gt;"-"),AND(L66&gt;1,L66&lt;&gt;"-"),AND(M66&gt;1,M66&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="N66:N72" si="8">IF(OR(AND(J66&gt;1,J66&lt;&gt;"-"),AND(K66&gt;1,K66&lt;&gt;"-"),AND(L66&gt;1,L66&lt;&gt;"-"),AND(M66&gt;1,M66&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -31767,6 +32253,141 @@
         <v>0</v>
       </c>
       <c r="N69" s="17" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N70" s="17" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N71" s="17" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J72" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N72" s="17" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -31875,7 +32496,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K57 K59 K61 K63 K65 K67">
+  <conditionalFormatting sqref="K59 K57 K61 K63 K65 K67">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -31947,7 +32568,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M57 M59 M61 M63 M65 M67 M69">
+  <conditionalFormatting sqref="M59 M57 M61 M63 M65 M67 M69">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -31960,11 +32581,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L54">
-    <cfRule type="containsText" dxfId="31" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L57 L59 L61 L63 L65 L67 L69">
+  <conditionalFormatting sqref="L59 L57 L61 L63 L65 L67 L69">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -31977,56 +32598,56 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K54">
-    <cfRule type="containsText" dxfId="30" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L57 L59 L61 L63 L65 L67 L69">
-    <cfRule type="containsText" dxfId="29" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K57 K59 K61 K63 K65 K67">
-    <cfRule type="containsText" dxfId="28" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M55">
-    <cfRule type="containsText" dxfId="27" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L55">
-    <cfRule type="containsText" dxfId="26" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55">
-    <cfRule type="containsText" dxfId="25" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M56">
-    <cfRule type="containsText" dxfId="24" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L56">
-    <cfRule type="containsText" dxfId="23" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K56">
-    <cfRule type="containsText" dxfId="22" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M57 M59 M61 M63 M65 M67 M69">
-    <cfRule type="containsText" dxfId="21" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M60 M58 M62 M64 M66 M68">
+  <conditionalFormatting sqref="M58 M60 M62 M64 M66 M68">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32038,7 +32659,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L60 L58 L62 L64 L66 L68">
+  <conditionalFormatting sqref="L58 L60 L62 L64 L66 L68">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32050,7 +32671,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K60 K58 K62 K64 K66 K68">
+  <conditionalFormatting sqref="K58 K60 K62 K64 K66 K68">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32063,41 +32684,41 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M58 M60 M62 M64 M66 M68">
-    <cfRule type="containsText" dxfId="20" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L58 L60 L62 L64 L66 L68">
-    <cfRule type="containsText" dxfId="19" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58 K60 K62 K64 K66 K68">
-    <cfRule type="containsText" dxfId="18" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M51">
-    <cfRule type="containsText" dxfId="17" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M52">
-    <cfRule type="containsText" dxfId="16" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M53">
-    <cfRule type="containsText" dxfId="15" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M54">
-    <cfRule type="containsText" dxfId="14" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J60 J58 J62 J64 J66 J68">
+  <conditionalFormatting sqref="J58 J60 J62 J64 J66 J68">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32110,12 +32731,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J58 J60 J62 J64 J66 J68">
-    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J57 J59 J61 J63 J65 J67 J69">
-    <cfRule type="containsText" dxfId="12" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32127,7 +32748,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DFFDBE4-EDF0-4B1F-97C7-5D3867DE7407}">
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -32140,30 +32761,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="44" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="48" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="51"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -35116,7 +35737,7 @@
         <v>0</v>
       </c>
       <c r="N67" s="17" t="str">
-        <f t="shared" ref="N67:N68" si="2">IF(OR(AND(J67&gt;1,J67&lt;&gt;"-"),AND(K67&gt;1,K67&lt;&gt;"-"),AND(L67&gt;1,L67&lt;&gt;"-"),AND(M67&gt;1,M67&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="N67:N71" si="2">IF(OR(AND(J67&gt;1,J67&lt;&gt;"-"),AND(K67&gt;1,K67&lt;&gt;"-"),AND(L67&gt;1,L67&lt;&gt;"-"),AND(M67&gt;1,M67&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -35159,6 +35780,141 @@
         <v>0</v>
       </c>
       <c r="N68" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I69" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J69" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N69" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N70" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N71" s="17" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -35208,17 +35964,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L66 L68">
-    <cfRule type="containsText" dxfId="11" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K66">
-    <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M66 M68">
-    <cfRule type="containsText" dxfId="9" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35259,17 +36015,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M65 M67">
-    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65 K67">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35286,7 +36042,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J66 J68">
-    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="2" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35303,7 +36059,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35320,7 +36076,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K68">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35374,7 +36130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1237A6-E42A-4384-BA92-D8D6967266F3}">
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -35387,28 +36143,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="32" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="35" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -38482,6 +39238,123 @@
       </c>
       <c r="L82" s="17" t="str">
         <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I83" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J83" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L83" s="17" t="str">
+        <f t="shared" ref="L83:L85" si="8">IF(OR(AND(I83&gt;1,I83&lt;&gt;"-"),AND(J83&gt;1,J83&lt;&gt;"-"),AND(K83&gt;1,K83&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H84" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I84" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J84" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L84" s="17" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H85" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I85" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J85" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L85" s="17" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -38506,7 +39379,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3 J5 J7 J9 J11">
-    <cfRule type="containsText" dxfId="774" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="771" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38631,7 +39504,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="773" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="770" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38648,12 +39521,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3 K5 K7 K9 K11">
-    <cfRule type="containsText" dxfId="772" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="769" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6 K8 K10">
-    <cfRule type="containsText" dxfId="771" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="768" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38670,7 +39543,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6 J8 J10">
-    <cfRule type="containsText" dxfId="770" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="767" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38687,7 +39560,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="769" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="766" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38704,7 +39577,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13:J14">
-    <cfRule type="containsText" dxfId="768" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="765" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38721,47 +39594,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="767" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="764" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="766" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="763" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19">
-    <cfRule type="containsText" dxfId="765" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="762" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="764" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="761" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="763" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="760" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19">
-    <cfRule type="containsText" dxfId="762" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="759" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="761" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="758" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="760" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="757" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="containsText" dxfId="759" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="756" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38778,7 +39651,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23">
-    <cfRule type="containsText" dxfId="758" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="755" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38795,7 +39668,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="757" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="754" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38812,7 +39685,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21">
-    <cfRule type="containsText" dxfId="756" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="753" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38829,7 +39702,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="containsText" dxfId="755" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="752" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38846,7 +39719,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25">
-    <cfRule type="containsText" dxfId="754" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="751" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38863,7 +39736,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27">
-    <cfRule type="containsText" dxfId="753" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="750" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38880,7 +39753,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29">
-    <cfRule type="containsText" dxfId="752" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="749" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38897,7 +39770,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="containsText" dxfId="751" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="748" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38914,7 +39787,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I33">
-    <cfRule type="containsText" dxfId="750" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="747" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38931,7 +39804,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29">
-    <cfRule type="containsText" dxfId="749" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="746" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38948,7 +39821,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31">
-    <cfRule type="containsText" dxfId="748" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="745" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38965,7 +39838,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31">
-    <cfRule type="containsText" dxfId="747" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="744" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38982,7 +39855,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33:J34">
-    <cfRule type="containsText" dxfId="746" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="743" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38999,7 +39872,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I36">
-    <cfRule type="containsText" dxfId="745" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="742" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39016,7 +39889,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J36">
-    <cfRule type="containsText" dxfId="744" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="741" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39033,7 +39906,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38">
-    <cfRule type="containsText" dxfId="743" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="740" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39045,7 +39918,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEF72CB-8B53-40A0-8E88-11E56C5C2BE2}">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -39058,28 +39931,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="41"/>
       <c r="E1" s="23"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="35" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -41793,6 +42666,123 @@
       </c>
       <c r="L73" s="17" t="str">
         <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I74" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J74" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L74" s="17" t="str">
+        <f t="shared" ref="L74:L76" si="7">IF(OR(AND(I74&gt;1,I74&lt;&gt;"-"),AND(J74&gt;1,J74&lt;&gt;"-"),AND(K74&gt;1,K74&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I75" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J75" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L75" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I76" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J76" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L76" s="17" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -41817,7 +42807,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="containsText" dxfId="742" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="739" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41930,7 +42920,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J10">
-    <cfRule type="containsText" dxfId="741" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="738" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41947,12 +42937,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10">
-    <cfRule type="containsText" dxfId="740" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="737" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="739" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="736" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41969,12 +42959,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="738" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="735" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="737" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="734" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41991,7 +42981,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="736" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="733" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42008,37 +42998,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="735" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="732" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="734" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="731" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="containsText" dxfId="733" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="730" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16">
-    <cfRule type="containsText" dxfId="732" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="729" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="containsText" dxfId="731" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="728" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="730" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="727" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17">
-    <cfRule type="containsText" dxfId="729" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="726" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42055,7 +43045,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19">
-    <cfRule type="containsText" dxfId="728" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="725" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42072,7 +43062,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19">
-    <cfRule type="containsText" dxfId="727" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="724" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42101,12 +43091,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11">
-    <cfRule type="containsText" dxfId="726" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="723" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="containsText" dxfId="725" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="722" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42123,7 +43113,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="724" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="721" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42164,17 +43154,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="723" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="720" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="722" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="719" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="721" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="718" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42203,12 +43193,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="720" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="717" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21">
-    <cfRule type="containsText" dxfId="719" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="716" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42220,7 +43210,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C490E5BC-33AC-4A3F-B53F-5B3EDDF611A7}">
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -42234,30 +43224,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="32" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="35" t="s">
+      <c r="I1" s="34"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -45988,6 +46978,141 @@
       </c>
       <c r="N88" s="17" t="str">
         <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K89" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L89" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M89" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N89" s="17" t="str">
+        <f t="shared" ref="N89:N91" si="20">IF(OR(AND(K89&gt;1,K89&lt;&gt;"-"),AND(L89&gt;1,L89&lt;&gt;"-"),AND(M89&gt;1,M89&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K90" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L90" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M90" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N90" s="17" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F91" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J91" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K91" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L91" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M91" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N91" s="17" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -46012,7 +47137,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7 K9 K12 K23">
-    <cfRule type="containsText" dxfId="718" priority="209" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="715" priority="209" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46125,7 +47250,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3 L5 L7 L9 L12">
-    <cfRule type="containsText" dxfId="717" priority="207" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="714" priority="207" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46142,7 +47267,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3 M5 M7 M9 M12">
-    <cfRule type="containsText" dxfId="716" priority="205" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="713" priority="205" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46159,7 +47284,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8 K11 K26">
-    <cfRule type="containsText" dxfId="715" priority="203" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="712" priority="203" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46176,7 +47301,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4 L6 L8 L11 L26">
-    <cfRule type="containsText" dxfId="714" priority="201" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="711" priority="201" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46193,7 +47318,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6 M8 M11">
-    <cfRule type="containsText" dxfId="713" priority="199" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="710" priority="199" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46210,47 +47335,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13">
-    <cfRule type="containsText" dxfId="712" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="709" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21">
-    <cfRule type="containsText" dxfId="711" priority="175" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="708" priority="175" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21">
-    <cfRule type="containsText" dxfId="710" priority="173" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="707" priority="173" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14">
-    <cfRule type="containsText" dxfId="709" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="706" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L17">
-    <cfRule type="containsText" dxfId="708" priority="185" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="705" priority="185" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M14">
-    <cfRule type="containsText" dxfId="707" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="704" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="containsText" dxfId="706" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="703" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="containsText" dxfId="705" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="702" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M17">
-    <cfRule type="containsText" dxfId="704" priority="183" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="701" priority="183" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46267,7 +47392,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10">
-    <cfRule type="containsText" dxfId="703" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="700" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46284,7 +47409,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="702" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="699" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46301,7 +47426,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13">
-    <cfRule type="containsText" dxfId="701" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="698" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46330,12 +47455,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M15">
-    <cfRule type="containsText" dxfId="700" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="697" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16">
-    <cfRule type="containsText" dxfId="699" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="696" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46376,17 +47501,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="698" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="695" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24">
-    <cfRule type="containsText" dxfId="697" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="694" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18">
-    <cfRule type="containsText" dxfId="696" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="693" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46403,7 +47528,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L15">
-    <cfRule type="containsText" dxfId="695" priority="149" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="692" priority="149" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46444,17 +47569,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18">
-    <cfRule type="containsText" dxfId="694" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="691" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19">
-    <cfRule type="containsText" dxfId="693" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="690" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18">
-    <cfRule type="containsText" dxfId="692" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="689" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46483,12 +47608,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="containsText" dxfId="691" priority="117" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="688" priority="117" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="containsText" dxfId="690" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="687" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46505,7 +47630,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23">
-    <cfRule type="containsText" dxfId="689" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="686" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46522,7 +47647,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21">
-    <cfRule type="containsText" dxfId="688" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="685" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46539,7 +47664,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L29">
-    <cfRule type="containsText" dxfId="687" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="684" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46556,7 +47681,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29">
-    <cfRule type="containsText" dxfId="686" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="683" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46585,12 +47710,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="685" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="682" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="containsText" dxfId="684" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="681" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46607,7 +47732,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="containsText" dxfId="683" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="680" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46636,12 +47761,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L32">
-    <cfRule type="containsText" dxfId="682" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="679" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L36">
-    <cfRule type="containsText" dxfId="681" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="678" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46670,12 +47795,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M36">
-    <cfRule type="containsText" dxfId="680" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="677" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M29">
-    <cfRule type="containsText" dxfId="679" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="676" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46692,7 +47817,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M34">
-    <cfRule type="containsText" dxfId="678" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="675" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46721,12 +47846,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="containsText" dxfId="677" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="674" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L38">
-    <cfRule type="containsText" dxfId="676" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="673" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46743,7 +47868,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32">
-    <cfRule type="containsText" dxfId="675" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="672" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46772,12 +47897,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36">
-    <cfRule type="containsText" dxfId="674" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="671" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L34">
-    <cfRule type="containsText" dxfId="673" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="670" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46794,7 +47919,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="containsText" dxfId="672" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="669" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46811,7 +47936,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37">
-    <cfRule type="containsText" dxfId="671" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="668" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46840,12 +47965,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="containsText" dxfId="670" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="667" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L37">
-    <cfRule type="containsText" dxfId="669" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="666" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46862,7 +47987,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M42">
-    <cfRule type="containsText" dxfId="668" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="665" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46891,12 +48016,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="containsText" dxfId="667" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="664" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L41">
-    <cfRule type="containsText" dxfId="666" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="663" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46913,7 +48038,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M39">
-    <cfRule type="containsText" dxfId="665" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="662" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46930,7 +48055,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40">
-    <cfRule type="containsText" dxfId="664" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="661" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46947,7 +48072,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L42">
-    <cfRule type="containsText" dxfId="663" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="660" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46964,7 +48089,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M41">
-    <cfRule type="containsText" dxfId="662" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="659" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46981,7 +48106,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L44">
-    <cfRule type="containsText" dxfId="661" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="658" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46998,7 +48123,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="containsText" dxfId="660" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="657" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47015,7 +48140,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K51">
-    <cfRule type="containsText" dxfId="659" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="656" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47032,7 +48157,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44">
-    <cfRule type="containsText" dxfId="658" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="655" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47049,7 +48174,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M44">
-    <cfRule type="containsText" dxfId="657" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="654" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47066,7 +48191,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L46">
-    <cfRule type="containsText" dxfId="656" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="653" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47083,7 +48208,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K46">
-    <cfRule type="containsText" dxfId="655" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="652" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47100,7 +48225,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M46">
-    <cfRule type="containsText" dxfId="654" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="651" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47117,7 +48242,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K48">
-    <cfRule type="containsText" dxfId="653" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="650" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47134,7 +48259,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49">
-    <cfRule type="containsText" dxfId="652" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="649" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47151,7 +48276,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49">
-    <cfRule type="containsText" dxfId="651" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="648" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47168,7 +48293,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M48">
-    <cfRule type="containsText" dxfId="650" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="647" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47185,7 +48310,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M50">
-    <cfRule type="containsText" dxfId="649" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="646" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47202,7 +48327,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L56">
-    <cfRule type="containsText" dxfId="648" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="645" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47219,7 +48344,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52">
-    <cfRule type="containsText" dxfId="647" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="644" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47236,7 +48361,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M52">
-    <cfRule type="containsText" dxfId="646" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="643" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47253,7 +48378,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K53 K55 K57 K59">
-    <cfRule type="containsText" dxfId="645" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="642" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47270,7 +48395,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M53 M55 M59">
-    <cfRule type="containsText" dxfId="644" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="641" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47287,7 +48412,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M54 M56 M58">
-    <cfRule type="containsText" dxfId="643" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="640" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47304,7 +48429,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L51">
-    <cfRule type="containsText" dxfId="642" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="639" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47321,7 +48446,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K54 K56 K58 K60">
-    <cfRule type="containsText" dxfId="641" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="638" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47338,7 +48463,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L57">
-    <cfRule type="containsText" dxfId="640" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="637" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47350,7 +48475,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E07B2820-C531-4BB9-BB49-09F9FB9ACBD1}">
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -47363,33 +48488,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="44" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="35" t="s">
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -51927,6 +53052,168 @@
       </c>
       <c r="Q87" s="17" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G88" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H88" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J88" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K88" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L88" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M88" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N88" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O88" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P88" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="17" t="str">
+        <f t="shared" ref="Q88:Q90" si="3">IF(OR(AND(L88&gt;1,L88&lt;&gt;"-"),AND(M88&gt;1,M88&lt;&gt;"-"),AND(N88&gt;1,N88&lt;&gt;"-"),AND(O88&gt;1,O88&lt;&gt;"-"),AND(P88&gt;1,P88&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K89" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L89" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M89" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N89" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O89" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P89" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="17" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K90" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L90" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M90" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N90" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O90" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P90" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="17" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -51951,7 +53238,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9 L12">
-    <cfRule type="containsText" dxfId="639" priority="237" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="636" priority="237" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52052,7 +53339,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3 M9 M12">
-    <cfRule type="containsText" dxfId="638" priority="235" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="635" priority="235" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52069,7 +53356,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3 N9 N12">
-    <cfRule type="containsText" dxfId="637" priority="233" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="634" priority="233" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52086,7 +53373,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8 L10 L25">
-    <cfRule type="containsText" dxfId="636" priority="231" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="633" priority="231" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52103,7 +53390,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6 M8 M10 M25">
-    <cfRule type="containsText" dxfId="635" priority="229" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="632" priority="229" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52120,7 +53407,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="containsText" dxfId="634" priority="227" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="631" priority="227" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52137,7 +53424,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M15">
-    <cfRule type="containsText" dxfId="633" priority="219" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="630" priority="219" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52154,42 +53441,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N15">
-    <cfRule type="containsText" dxfId="632" priority="217" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="629" priority="217" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18">
-    <cfRule type="containsText" dxfId="631" priority="207" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="628" priority="207" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18">
-    <cfRule type="containsText" dxfId="630" priority="205" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="627" priority="205" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L15">
-    <cfRule type="containsText" dxfId="629" priority="221" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="626" priority="221" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L16">
-    <cfRule type="containsText" dxfId="628" priority="215" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="625" priority="215" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16">
-    <cfRule type="containsText" dxfId="627" priority="213" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="624" priority="213" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16">
-    <cfRule type="containsText" dxfId="626" priority="211" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="623" priority="211" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18">
-    <cfRule type="containsText" dxfId="625" priority="209" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="622" priority="209" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52206,7 +53493,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5">
-    <cfRule type="containsText" dxfId="624" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="621" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52223,7 +53510,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="containsText" dxfId="623" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="620" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52240,7 +53527,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="containsText" dxfId="622" priority="199" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="619" priority="199" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52257,7 +53544,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5">
-    <cfRule type="containsText" dxfId="621" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="618" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52274,7 +53561,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="containsText" dxfId="620" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="617" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52291,7 +53578,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7">
-    <cfRule type="containsText" dxfId="619" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="616" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52308,7 +53595,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7">
-    <cfRule type="containsText" dxfId="618" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="615" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52349,17 +53636,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14">
-    <cfRule type="containsText" dxfId="617" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="614" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M14">
-    <cfRule type="containsText" dxfId="616" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="613" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11">
-    <cfRule type="containsText" dxfId="615" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="612" priority="179" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52376,7 +53663,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N14">
-    <cfRule type="containsText" dxfId="614" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="611" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52393,7 +53680,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13">
-    <cfRule type="containsText" dxfId="613" priority="177" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="610" priority="177" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52434,17 +53721,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L17">
-    <cfRule type="containsText" dxfId="612" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="609" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19">
-    <cfRule type="containsText" dxfId="611" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="608" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19">
-    <cfRule type="containsText" dxfId="610" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="607" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52485,17 +53772,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21">
-    <cfRule type="containsText" dxfId="609" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="606" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21">
-    <cfRule type="containsText" dxfId="608" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="605" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19">
-    <cfRule type="containsText" dxfId="607" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="604" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52512,7 +53799,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="containsText" dxfId="606" priority="141" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="603" priority="141" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52529,7 +53816,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21">
-    <cfRule type="containsText" dxfId="605" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="602" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52546,7 +53833,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="containsText" dxfId="604" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="601" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52575,12 +53862,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L35">
-    <cfRule type="containsText" dxfId="603" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="600" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="602" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="599" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52597,7 +53884,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="containsText" dxfId="601" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="598" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52626,12 +53913,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L28">
-    <cfRule type="containsText" dxfId="600" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="597" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M28">
-    <cfRule type="containsText" dxfId="599" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="596" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52648,7 +53935,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N28">
-    <cfRule type="containsText" dxfId="598" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="595" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52677,12 +53964,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L30">
-    <cfRule type="containsText" dxfId="597" priority="125" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="594" priority="125" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M30">
-    <cfRule type="containsText" dxfId="596" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="593" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52699,7 +53986,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N30">
-    <cfRule type="containsText" dxfId="595" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="592" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52716,7 +54003,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35">
-    <cfRule type="containsText" dxfId="594" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="591" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52733,7 +54020,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:N31">
-    <cfRule type="containsText" dxfId="593" priority="117" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="590" priority="117" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52750,7 +54037,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32">
-    <cfRule type="containsText" dxfId="592" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="589" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52767,7 +54054,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33">
-    <cfRule type="containsText" dxfId="591" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="588" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52784,7 +54071,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33">
-    <cfRule type="containsText" dxfId="590" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="587" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52801,7 +54088,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L34">
-    <cfRule type="containsText" dxfId="589" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="586" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52818,7 +54105,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M40:M41 M43 M51 M61:M63">
-    <cfRule type="containsText" dxfId="588" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="585" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52835,7 +54122,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M34:N34">
-    <cfRule type="containsText" dxfId="587" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="584" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52864,12 +54151,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40:L41 L43 L57:L58 L62">
-    <cfRule type="containsText" dxfId="586" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="583" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35">
-    <cfRule type="containsText" dxfId="585" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="582" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52886,7 +54173,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L36">
-    <cfRule type="containsText" dxfId="584" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="581" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52903,7 +54190,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N36">
-    <cfRule type="containsText" dxfId="583" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="580" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52920,7 +54207,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M36">
-    <cfRule type="containsText" dxfId="582" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="579" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52937,7 +54224,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="containsText" dxfId="581" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="578" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52954,7 +54241,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M38">
-    <cfRule type="containsText" dxfId="580" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="577" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52971,7 +54258,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N38">
-    <cfRule type="containsText" dxfId="579" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="576" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52988,7 +54275,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L39">
-    <cfRule type="containsText" dxfId="578" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="575" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53005,7 +54292,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N39">
-    <cfRule type="containsText" dxfId="577" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="574" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53022,7 +54309,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N40:N41 N43:N44 N57 N61:N63">
-    <cfRule type="containsText" dxfId="576" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="573" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53039,7 +54326,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M42">
-    <cfRule type="containsText" dxfId="575" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="572" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53056,7 +54343,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L42">
-    <cfRule type="containsText" dxfId="574" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="571" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53073,7 +54360,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N42">
-    <cfRule type="containsText" dxfId="573" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="570" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53090,7 +54377,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M45">
-    <cfRule type="containsText" dxfId="572" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="569" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53107,7 +54394,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="containsText" dxfId="571" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="568" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53124,7 +54411,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N45:N46">
-    <cfRule type="containsText" dxfId="570" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="567" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53141,7 +54428,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M48">
-    <cfRule type="containsText" dxfId="569" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="566" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53158,7 +54445,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L48">
-    <cfRule type="containsText" dxfId="568" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="565" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53175,7 +54462,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N48">
-    <cfRule type="containsText" dxfId="567" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="564" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53192,7 +54479,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M54">
-    <cfRule type="containsText" dxfId="566" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="563" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53209,7 +54496,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L54:L55">
-    <cfRule type="containsText" dxfId="565" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="562" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53226,7 +54513,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N54">
-    <cfRule type="containsText" dxfId="564" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="561" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53243,7 +54530,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L46">
-    <cfRule type="containsText" dxfId="563" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="560" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53260,7 +54547,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P46">
-    <cfRule type="containsText" dxfId="562" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="559" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53277,7 +54564,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N49">
-    <cfRule type="containsText" dxfId="561" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="558" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53294,7 +54581,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47">
-    <cfRule type="containsText" dxfId="560" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="557" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53311,7 +54598,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P50">
-    <cfRule type="containsText" dxfId="559" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="556" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53328,7 +54615,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O46">
-    <cfRule type="containsText" dxfId="558" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="555" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53345,7 +54632,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M46">
-    <cfRule type="containsText" dxfId="557" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="554" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53362,7 +54649,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N52">
-    <cfRule type="containsText" dxfId="556" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="553" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53379,7 +54666,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47">
-    <cfRule type="containsText" dxfId="555" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="552" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53396,7 +54683,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O53">
-    <cfRule type="containsText" dxfId="554" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="551" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53413,7 +54700,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O49">
-    <cfRule type="containsText" dxfId="553" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="550" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53430,7 +54717,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49">
-    <cfRule type="containsText" dxfId="552" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="549" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53447,7 +54734,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49">
-    <cfRule type="containsText" dxfId="551" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="548" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53464,7 +54751,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M52">
-    <cfRule type="containsText" dxfId="550" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="547" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53481,7 +54768,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P52">
-    <cfRule type="containsText" dxfId="549" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="546" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53498,7 +54785,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M56">
-    <cfRule type="containsText" dxfId="548" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="545" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53515,7 +54802,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52">
-    <cfRule type="containsText" dxfId="547" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="544" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53532,7 +54819,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N55">
-    <cfRule type="containsText" dxfId="546" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="543" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53549,7 +54836,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O55">
-    <cfRule type="containsText" dxfId="545" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="542" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53566,7 +54853,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O56">
-    <cfRule type="containsText" dxfId="544" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="541" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53583,7 +54870,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O61">
-    <cfRule type="containsText" dxfId="543" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="540" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53595,7 +54882,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD781A2-1BD3-49B0-B041-FFBB4C24B577}">
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -53608,28 +54895,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="32" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="35" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -56271,6 +57558,123 @@
       </c>
       <c r="L69" s="17" t="str">
         <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L70" s="17" t="str">
+        <f t="shared" ref="L70:L72" si="10">IF(OR(AND(I70&gt;1,I70&lt;&gt;"-"),AND(J70&gt;1,J70&lt;&gt;"-"),AND(K70&gt;1,K70&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L71" s="17" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J72" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L72" s="17" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -56427,7 +57831,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J29 J33 J35">
-    <cfRule type="containsText" dxfId="542" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="539" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56444,47 +57848,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29 K33 K35">
-    <cfRule type="containsText" dxfId="541" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="538" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="540" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="537" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="539" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="536" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32">
-    <cfRule type="containsText" dxfId="538" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="535" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="537" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="534" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="536" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="533" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30 K32 K34 K36">
-    <cfRule type="containsText" dxfId="535" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="532" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="534" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="531" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="containsText" dxfId="533" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="530" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56501,7 +57905,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16">
-    <cfRule type="containsText" dxfId="532" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="529" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56518,7 +57922,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="531" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="528" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56535,12 +57939,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29 I33 I35 I39 I41 I43">
-    <cfRule type="containsText" dxfId="530" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="527" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30 I32 I34 I36 I44">
-    <cfRule type="containsText" dxfId="529" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="526" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56557,7 +57961,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="containsText" dxfId="528" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="525" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56574,12 +57978,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31">
-    <cfRule type="containsText" dxfId="527" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="524" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31">
-    <cfRule type="containsText" dxfId="526" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="523" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56596,7 +58000,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="containsText" dxfId="525" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="522" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56613,7 +58017,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I37">
-    <cfRule type="containsText" dxfId="524" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="521" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56630,12 +58034,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="containsText" dxfId="523" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="520" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38">
-    <cfRule type="containsText" dxfId="522" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="519" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56647,7 +58051,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA9F1D4-3094-4668-81A4-73377285B7BF}">
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -56661,32 +58065,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="44" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="35" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="43"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="44"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -61671,6 +63075,159 @@
       </c>
       <c r="P101" s="17" t="str">
         <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P102" s="17" t="str">
+        <f t="shared" ref="P102:P104" si="5">IF(OR(AND(K102&gt;1,K102&lt;&gt;"-"),AND(L102&gt;1,L102&lt;&gt;"-"),AND(M102&gt;1,M102&lt;&gt;"-"),AND(N102&gt;1,N102&lt;&gt;"-"),AND(O102&gt;1,O102&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F103" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G103" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H103" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I103" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J103" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K103" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L103" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M103" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N103" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O103" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P103" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F104" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G104" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H104" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I104" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J104" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K104" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L104" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M104" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N104" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O104" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P104" s="17" t="str">
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -61755,7 +63312,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3 L5 L7 L9 L11">
-    <cfRule type="containsText" dxfId="521" priority="309" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="518" priority="309" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61772,12 +63329,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3 M5 M7 M9 M11">
-    <cfRule type="containsText" dxfId="520" priority="307" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="517" priority="307" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6 L8 L10 L18 L33 L39 L50 L55">
-    <cfRule type="containsText" dxfId="519" priority="303" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="516" priority="303" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61794,27 +63351,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6 M8 M10">
-    <cfRule type="containsText" dxfId="518" priority="301" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="515" priority="301" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L12">
-    <cfRule type="containsText" dxfId="517" priority="297" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="514" priority="297" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13">
-    <cfRule type="containsText" dxfId="516" priority="293" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="513" priority="293" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13">
-    <cfRule type="containsText" dxfId="515" priority="291" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="512" priority="291" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M14">
-    <cfRule type="containsText" dxfId="514" priority="285" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="511" priority="285" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61831,7 +63388,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12">
-    <cfRule type="containsText" dxfId="513" priority="273" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="510" priority="273" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61848,7 +63405,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33 K39 K43 K49:K50 K55 K61 K68">
-    <cfRule type="containsText" dxfId="512" priority="271" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="509" priority="271" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61865,7 +63422,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19 M26:M29 M39 M43 M49:M50 M53 M55 M58 M61 M68">
-    <cfRule type="containsText" dxfId="511" priority="269" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="508" priority="269" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61882,7 +63439,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21">
-    <cfRule type="containsText" dxfId="510" priority="261" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="507" priority="261" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61899,7 +63456,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21">
-    <cfRule type="containsText" dxfId="509" priority="259" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="506" priority="259" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61916,7 +63473,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20">
-    <cfRule type="containsText" dxfId="508" priority="249" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="505" priority="249" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61933,7 +63490,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L22">
-    <cfRule type="containsText" dxfId="507" priority="247" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="504" priority="247" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61950,7 +63507,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L24">
-    <cfRule type="containsText" dxfId="506" priority="245" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="503" priority="245" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61967,7 +63524,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24">
-    <cfRule type="containsText" dxfId="505" priority="243" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="502" priority="243" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61984,7 +63541,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24">
-    <cfRule type="containsText" dxfId="504" priority="241" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="501" priority="241" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62001,7 +63558,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28">
-    <cfRule type="containsText" dxfId="503" priority="239" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="500" priority="239" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62018,7 +63575,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29">
-    <cfRule type="containsText" dxfId="502" priority="237" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="499" priority="237" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62035,7 +63592,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31">
-    <cfRule type="containsText" dxfId="501" priority="211" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="498" priority="211" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62052,7 +63609,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L32">
-    <cfRule type="containsText" dxfId="500" priority="229" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="497" priority="229" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62069,7 +63626,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="containsText" dxfId="499" priority="227" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="496" priority="227" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62086,7 +63643,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35">
-    <cfRule type="containsText" dxfId="498" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="495" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62103,7 +63660,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L37">
-    <cfRule type="containsText" dxfId="497" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="494" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62120,7 +63677,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="containsText" dxfId="496" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="493" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62137,7 +63694,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L36">
-    <cfRule type="containsText" dxfId="495" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="492" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62154,7 +63711,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36">
-    <cfRule type="containsText" dxfId="494" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="491" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62171,7 +63728,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40">
-    <cfRule type="containsText" dxfId="493" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="490" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62188,7 +63745,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L41">
-    <cfRule type="containsText" dxfId="492" priority="185" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="489" priority="185" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62205,7 +63762,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L44">
-    <cfRule type="containsText" dxfId="491" priority="183" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="488" priority="183" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62222,7 +63779,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="containsText" dxfId="490" priority="181" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="487" priority="181" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62239,7 +63796,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L47">
-    <cfRule type="containsText" dxfId="489" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="486" priority="179" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62256,7 +63813,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47">
-    <cfRule type="containsText" dxfId="488" priority="177" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="485" priority="177" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62273,7 +63830,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47">
-    <cfRule type="containsText" dxfId="487" priority="175" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="484" priority="175" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62290,7 +63847,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L51">
-    <cfRule type="containsText" dxfId="486" priority="173" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="483" priority="173" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62307,7 +63864,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52">
-    <cfRule type="containsText" dxfId="485" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="482" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62324,7 +63881,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M52">
-    <cfRule type="containsText" dxfId="484" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="481" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62341,7 +63898,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L54">
-    <cfRule type="containsText" dxfId="483" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="480" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62358,7 +63915,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K54">
-    <cfRule type="containsText" dxfId="482" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="479" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62375,7 +63932,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M54">
-    <cfRule type="containsText" dxfId="481" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="478" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62392,7 +63949,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O55">
-    <cfRule type="containsText" dxfId="480" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="477" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62409,7 +63966,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L56">
-    <cfRule type="containsText" dxfId="479" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="476" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62426,7 +63983,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K56">
-    <cfRule type="containsText" dxfId="478" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="475" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62443,7 +64000,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M56">
-    <cfRule type="containsText" dxfId="477" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="474" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62460,7 +64017,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L57">
-    <cfRule type="containsText" dxfId="476" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="473" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62477,7 +64034,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K57">
-    <cfRule type="containsText" dxfId="475" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="472" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62494,7 +64051,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M57">
-    <cfRule type="containsText" dxfId="474" priority="149" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="471" priority="149" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62511,7 +64068,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60">
-    <cfRule type="containsText" dxfId="473" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="470" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62528,7 +64085,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L58">
-    <cfRule type="containsText" dxfId="472" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="469" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62545,7 +64102,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58">
-    <cfRule type="containsText" dxfId="471" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="468" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62562,7 +64119,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L59">
-    <cfRule type="containsText" dxfId="470" priority="141" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="467" priority="141" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62579,7 +64136,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K64">
-    <cfRule type="containsText" dxfId="469" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="466" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62596,7 +64153,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59">
-    <cfRule type="containsText" dxfId="468" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="465" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62613,7 +64170,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L62">
-    <cfRule type="containsText" dxfId="467" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="464" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62630,7 +64187,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K62">
-    <cfRule type="containsText" dxfId="466" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="463" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62647,7 +64204,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M62">
-    <cfRule type="containsText" dxfId="465" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="462" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62664,7 +64221,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L64">
-    <cfRule type="containsText" dxfId="464" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="461" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62681,7 +64238,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64">
-    <cfRule type="containsText" dxfId="463" priority="125" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="460" priority="125" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62698,7 +64255,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L63">
-    <cfRule type="containsText" dxfId="462" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="459" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62715,7 +64272,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63">
-    <cfRule type="containsText" dxfId="461" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="458" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62732,7 +64289,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M63">
-    <cfRule type="containsText" dxfId="460" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="457" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62749,7 +64306,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N63:O63">
-    <cfRule type="containsText" dxfId="459" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="456" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62766,7 +64323,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N67">
-    <cfRule type="containsText" dxfId="458" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="455" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62783,7 +64340,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L66">
-    <cfRule type="containsText" dxfId="457" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="454" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62800,7 +64357,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L65">
-    <cfRule type="containsText" dxfId="456" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="453" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62817,7 +64374,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67">
-    <cfRule type="containsText" dxfId="455" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="452" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62834,7 +64391,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67">
-    <cfRule type="containsText" dxfId="454" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="451" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62851,7 +64408,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M79">
-    <cfRule type="containsText" dxfId="453" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="450" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62868,7 +64425,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N69">
-    <cfRule type="containsText" dxfId="452" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="449" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62885,7 +64442,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K69">
-    <cfRule type="containsText" dxfId="451" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="448" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62902,7 +64459,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L69">
-    <cfRule type="containsText" dxfId="450" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="447" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62919,7 +64476,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M69">
-    <cfRule type="containsText" dxfId="449" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="446" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62936,7 +64493,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80">
-    <cfRule type="containsText" dxfId="448" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="445" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62953,7 +64510,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L80">
-    <cfRule type="containsText" dxfId="447" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="444" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62970,7 +64527,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M80">
-    <cfRule type="containsText" dxfId="446" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="443" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62987,7 +64544,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K81">
-    <cfRule type="containsText" dxfId="445" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="442" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63004,7 +64561,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L81">
-    <cfRule type="containsText" dxfId="444" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="441" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63021,7 +64578,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M81">
-    <cfRule type="containsText" dxfId="443" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="440" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63038,7 +64595,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N70">
-    <cfRule type="containsText" dxfId="442" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="439" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63055,7 +64612,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K70">
-    <cfRule type="containsText" dxfId="441" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="438" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63072,7 +64629,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L70">
-    <cfRule type="containsText" dxfId="440" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="437" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63089,7 +64646,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M70">
-    <cfRule type="containsText" dxfId="439" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="436" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63106,7 +64663,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N71">
-    <cfRule type="containsText" dxfId="438" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="435" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63123,7 +64680,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K71">
-    <cfRule type="containsText" dxfId="437" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="434" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63140,7 +64697,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L71">
-    <cfRule type="containsText" dxfId="436" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="433" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63157,7 +64714,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M71">
-    <cfRule type="containsText" dxfId="435" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="432" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63174,7 +64731,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N72">
-    <cfRule type="containsText" dxfId="434" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="431" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63191,7 +64748,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K72">
-    <cfRule type="containsText" dxfId="433" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="430" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63208,7 +64765,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L72">
-    <cfRule type="containsText" dxfId="432" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="429" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63225,7 +64782,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M72">
-    <cfRule type="containsText" dxfId="431" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="428" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63242,7 +64799,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N73">
-    <cfRule type="containsText" dxfId="430" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="427" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63259,7 +64816,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K73">
-    <cfRule type="containsText" dxfId="429" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="426" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63276,7 +64833,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L73">
-    <cfRule type="containsText" dxfId="428" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="425" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63293,7 +64850,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M73">
-    <cfRule type="containsText" dxfId="427" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="424" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63310,7 +64867,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N74">
-    <cfRule type="containsText" dxfId="426" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="423" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63327,7 +64884,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K74">
-    <cfRule type="containsText" dxfId="425" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="422" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63344,7 +64901,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L74">
-    <cfRule type="containsText" dxfId="424" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="421" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63361,7 +64918,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M74">
-    <cfRule type="containsText" dxfId="423" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="420" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63378,7 +64935,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N75">
-    <cfRule type="containsText" dxfId="422" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="419" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63395,7 +64952,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K75">
-    <cfRule type="containsText" dxfId="421" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="418" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63412,7 +64969,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L75">
-    <cfRule type="containsText" dxfId="420" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="417" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63429,7 +64986,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M75">
-    <cfRule type="containsText" dxfId="419" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="416" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63446,7 +65003,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N76">
-    <cfRule type="containsText" dxfId="418" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="415" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63463,7 +65020,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76">
-    <cfRule type="containsText" dxfId="417" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="414" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63480,7 +65037,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L76">
-    <cfRule type="containsText" dxfId="416" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="413" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63497,7 +65054,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M76">
-    <cfRule type="containsText" dxfId="415" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="412" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63514,7 +65071,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N77">
-    <cfRule type="containsText" dxfId="414" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="411" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63531,7 +65088,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K77">
-    <cfRule type="containsText" dxfId="413" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="410" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63548,7 +65105,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L77">
-    <cfRule type="containsText" dxfId="412" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="409" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63565,7 +65122,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M77">
-    <cfRule type="containsText" dxfId="411" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="408" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63582,7 +65139,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N78">
-    <cfRule type="containsText" dxfId="410" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="407" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63599,7 +65156,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78">
-    <cfRule type="containsText" dxfId="409" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="406" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63616,7 +65173,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L78">
-    <cfRule type="containsText" dxfId="408" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="405" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63633,7 +65190,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M78">
-    <cfRule type="containsText" dxfId="407" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="404" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63650,7 +65207,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N79">
-    <cfRule type="containsText" dxfId="406" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="403" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63667,7 +65224,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="containsText" dxfId="405" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="402" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63684,7 +65241,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="containsText" dxfId="404" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="401" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63696,7 +65253,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137E3033-7857-400C-B5FF-133DA51F6E59}">
-  <dimension ref="A1:R80"/>
+  <dimension ref="A1:R83"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -63709,34 +65266,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="44" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="35" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
     </row>
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -68036,6 +69593,177 @@
       </c>
       <c r="R80" s="17" t="str">
         <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F81" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I81" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J81" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K81" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M81" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N81" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O81" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P81" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R81" s="17" t="str">
+        <f t="shared" ref="R81:R83" si="15">IF(OR(AND(L81&gt;1,L81&lt;&gt;"-"),AND(M81&gt;1,M81&lt;&gt;"-"),AND(N81&gt;1,N81&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G82" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H82" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I82" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J82" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K82" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L82" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N82" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O82" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P82" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R82" s="17" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L83" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="M83" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N83" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O83" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P83" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R83" s="17" t="str">
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -68156,17 +69884,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3 M7 M9">
-    <cfRule type="containsText" dxfId="403" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="400" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7 N9">
-    <cfRule type="containsText" dxfId="402" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="399" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6 M8">
-    <cfRule type="containsText" dxfId="401" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="398" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68183,7 +69911,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6 N8 N10">
-    <cfRule type="containsText" dxfId="400" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="397" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68200,7 +69928,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M14">
-    <cfRule type="containsText" dxfId="399" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="396" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68217,32 +69945,32 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13">
-    <cfRule type="containsText" dxfId="398" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="395" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16">
-    <cfRule type="containsText" dxfId="397" priority="141" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="394" priority="141" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16">
-    <cfRule type="containsText" dxfId="396" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="393" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N14:N15">
-    <cfRule type="containsText" dxfId="395" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="392" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="containsText" dxfId="394" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="391" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M17">
-    <cfRule type="containsText" dxfId="393" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="390" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68259,7 +69987,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N17">
-    <cfRule type="containsText" dxfId="392" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="389" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68276,12 +70004,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5">
-    <cfRule type="containsText" dxfId="391" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="388" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18">
-    <cfRule type="containsText" dxfId="390" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="387" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68298,7 +70026,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20">
-    <cfRule type="containsText" dxfId="389" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="386" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68315,7 +70043,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22">
-    <cfRule type="containsText" dxfId="388" priority="125" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="385" priority="125" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68332,7 +70060,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22">
-    <cfRule type="containsText" dxfId="387" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="384" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68349,7 +70077,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="containsText" dxfId="386" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="383" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68366,7 +70094,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="containsText" dxfId="385" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="382" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68383,7 +70111,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="containsText" dxfId="384" priority="117" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="381" priority="117" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68400,7 +70128,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24">
-    <cfRule type="containsText" dxfId="383" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="380" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68417,7 +70145,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="containsText" dxfId="382" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="379" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68434,7 +70162,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="containsText" dxfId="381" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="378" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68451,7 +70179,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="380" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="377" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68468,7 +70196,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L28">
-    <cfRule type="containsText" dxfId="379" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="376" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68485,7 +70213,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N28">
-    <cfRule type="containsText" dxfId="378" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="375" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68502,7 +70230,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M28">
-    <cfRule type="containsText" dxfId="377" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="374" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68519,7 +70247,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L30">
-    <cfRule type="containsText" dxfId="376" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="373" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68536,7 +70264,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N30">
-    <cfRule type="containsText" dxfId="375" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="372" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68553,7 +70281,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M30">
-    <cfRule type="containsText" dxfId="374" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="371" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68570,7 +70298,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32">
-    <cfRule type="containsText" dxfId="373" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="370" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68587,17 +70315,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32">
-    <cfRule type="containsText" dxfId="372" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="369" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N39">
-    <cfRule type="containsText" dxfId="371" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="368" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N40 N42 N44:N45">
-    <cfRule type="containsText" dxfId="370" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="367" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68614,7 +70342,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35">
-    <cfRule type="containsText" dxfId="369" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="366" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68631,7 +70359,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35">
-    <cfRule type="containsText" dxfId="368" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="365" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68660,7 +70388,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O41">
-    <cfRule type="containsText" dxfId="367" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="364" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68677,7 +70405,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40:M40 L44:M44 M48">
-    <cfRule type="containsText" dxfId="366" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="363" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68694,7 +70422,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N41 N43 N46">
-    <cfRule type="containsText" dxfId="365" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="362" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68711,7 +70439,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L41:M41 L43:M43 L46:M46">
-    <cfRule type="containsText" dxfId="364" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="361" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68728,7 +70456,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q45">
-    <cfRule type="containsText" dxfId="363" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="360" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68745,7 +70473,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M45">
-    <cfRule type="containsText" dxfId="362" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="359" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68762,7 +70490,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="containsText" dxfId="361" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="358" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68779,7 +70507,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P45">
-    <cfRule type="containsText" dxfId="360" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="357" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68796,7 +70524,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47">
-    <cfRule type="containsText" dxfId="359" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="356" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68813,7 +70541,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L47:M47">
-    <cfRule type="containsText" dxfId="358" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="355" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68830,7 +70558,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47">
-    <cfRule type="containsText" dxfId="357" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="354" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68847,7 +70575,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N49 N51 N53 N55 N57 N59 N61 N65">
-    <cfRule type="containsText" dxfId="356" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="353" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68864,7 +70592,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49:M49 L51:M51 L53:M53 L55:M55 L57:M57 L59:M59 L61:M61">
-    <cfRule type="containsText" dxfId="355" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="352" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68881,7 +70609,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P49 P51 P53 P55 P57 P59 P65">
-    <cfRule type="containsText" dxfId="354" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="351" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68898,7 +70626,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50 N52 N54 N56 N58 N60">
-    <cfRule type="containsText" dxfId="353" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="350" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68915,7 +70643,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L50:M50 L52:M52 L54:M54 L56:M56 L58:M58 L60:M60">
-    <cfRule type="containsText" dxfId="352" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="349" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68932,7 +70660,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P50 P52 P54 P56 P58 P60">
-    <cfRule type="containsText" dxfId="351" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="348" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68949,7 +70677,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61">
-    <cfRule type="containsText" dxfId="350" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="347" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68966,7 +70694,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N66">
-    <cfRule type="containsText" dxfId="349" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="346" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68983,7 +70711,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P66">
-    <cfRule type="containsText" dxfId="348" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="345" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69000,7 +70728,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M66">
-    <cfRule type="containsText" dxfId="347" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="344" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69017,7 +70745,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N74">
-    <cfRule type="containsText" dxfId="346" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="343" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69034,7 +70762,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N67">
-    <cfRule type="containsText" dxfId="345" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="342" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69051,7 +70779,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M69">
-    <cfRule type="containsText" dxfId="344" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="341" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69068,7 +70796,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M67">
-    <cfRule type="containsText" dxfId="343" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="340" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69085,7 +70813,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N71">
-    <cfRule type="containsText" dxfId="342" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="339" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69102,7 +70830,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N68">
-    <cfRule type="containsText" dxfId="341" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="338" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69119,7 +70847,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N73">
-    <cfRule type="containsText" dxfId="340" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="337" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69136,7 +70864,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N69">
-    <cfRule type="containsText" dxfId="339" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="336" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69153,7 +70881,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L69">
-    <cfRule type="containsText" dxfId="338" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="335" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69177,7 +70905,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3001186-9460-468F-8F8C-A3E080BA5200}">
-  <dimension ref="A1:Y99"/>
+  <dimension ref="A1:Y102"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -69190,40 +70918,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="44" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="35" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
+      <c r="W1" s="44"/>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
@@ -76464,6 +78192,231 @@
       </c>
       <c r="X99" s="17" t="str">
         <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="M100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="N100" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="O100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="S100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="T100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="U100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="V100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="W100" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="X100" s="17" t="str">
+        <f t="shared" ref="X100:X102" si="8">IF(OR(AND(O100&gt;1,O100&lt;&gt;"-"),AND(P100&gt;1,P100&lt;&gt;"-"),AND(Q100&gt;1,Q100&lt;&gt;"-"),AND(S100&gt;1,S100&lt;&gt;"-"),AND(T100&gt;1,T100&lt;&gt;"-"),AND(U100&gt;1,U100&lt;&gt;"-"),AND(V100&gt;1,V100&lt;&gt;"-"),AND(W100&gt;1,W100&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="M101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="N101" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="O101" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P101" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R101" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="S101" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="T101" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="U101" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="V101" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="W101" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="X101" s="17" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="M102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="N102" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="O102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="S102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="T102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="U102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="V102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="W102" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="X102" s="17" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -76500,12 +78453,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8">
-    <cfRule type="containsText" dxfId="337" priority="263" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="334" priority="263" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q8">
-    <cfRule type="containsText" dxfId="336" priority="261" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="333" priority="261" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76534,7 +78487,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P16">
-    <cfRule type="containsText" dxfId="335" priority="233" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="332" priority="233" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76551,7 +78504,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P22">
-    <cfRule type="containsText" dxfId="334" priority="229" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="331" priority="229" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76568,7 +78521,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q22">
-    <cfRule type="containsText" dxfId="333" priority="227" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="330" priority="227" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76585,7 +78538,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q23">
-    <cfRule type="containsText" dxfId="332" priority="225" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="329" priority="225" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76602,7 +78555,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P24">
-    <cfRule type="containsText" dxfId="331" priority="223" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="328" priority="223" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76619,7 +78572,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26">
-    <cfRule type="containsText" dxfId="330" priority="221" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="327" priority="221" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76636,12 +78589,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q26">
-    <cfRule type="containsText" dxfId="329" priority="219" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="326" priority="219" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P28">
-    <cfRule type="containsText" dxfId="328" priority="217" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="325" priority="217" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76658,7 +78611,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P32">
-    <cfRule type="containsText" dxfId="327" priority="215" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="324" priority="215" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76675,7 +78628,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q32">
-    <cfRule type="containsText" dxfId="326" priority="213" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="323" priority="213" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76692,7 +78645,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P33">
-    <cfRule type="containsText" dxfId="325" priority="211" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="322" priority="211" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76709,7 +78662,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q33">
-    <cfRule type="containsText" dxfId="324" priority="209" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="321" priority="209" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76726,7 +78679,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P35">
-    <cfRule type="containsText" dxfId="323" priority="203" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="320" priority="203" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76743,7 +78696,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q35">
-    <cfRule type="containsText" dxfId="322" priority="201" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="319" priority="201" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76760,7 +78713,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="containsText" dxfId="321" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="318" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76777,7 +78730,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P39">
-    <cfRule type="containsText" dxfId="320" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="317" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76794,7 +78747,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37">
-    <cfRule type="containsText" dxfId="319" priority="199" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="316" priority="199" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76811,7 +78764,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P41 P43 P45">
-    <cfRule type="containsText" dxfId="318" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="315" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76828,7 +78781,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q41 Q43 Q45">
-    <cfRule type="containsText" dxfId="317" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="314" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76845,7 +78798,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40 Q44 Q49">
-    <cfRule type="containsText" dxfId="316" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="313" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76862,7 +78815,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P40 P44">
-    <cfRule type="containsText" dxfId="315" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="312" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76879,7 +78832,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O41">
-    <cfRule type="containsText" dxfId="314" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="311" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76896,7 +78849,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q42">
-    <cfRule type="containsText" dxfId="313" priority="177" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="310" priority="177" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76913,7 +78866,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S42">
-    <cfRule type="containsText" dxfId="312" priority="175" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="309" priority="175" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76930,7 +78883,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42">
-    <cfRule type="containsText" dxfId="311" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="308" priority="179" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76947,12 +78900,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T42">
-    <cfRule type="containsText" dxfId="310" priority="173" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="307" priority="173" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O44">
-    <cfRule type="containsText" dxfId="309" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="306" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76969,7 +78922,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O43">
-    <cfRule type="containsText" dxfId="308" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="305" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76998,7 +78951,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q46">
-    <cfRule type="containsText" dxfId="307" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="304" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77015,7 +78968,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O45">
-    <cfRule type="containsText" dxfId="306" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="303" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77032,7 +78985,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R45">
-    <cfRule type="containsText" dxfId="305" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="302" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77049,7 +79002,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47">
-    <cfRule type="containsText" dxfId="304" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="301" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77066,7 +79019,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P48">
-    <cfRule type="containsText" dxfId="303" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="300" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77083,7 +79036,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q50">
-    <cfRule type="containsText" dxfId="302" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="299" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77100,7 +79053,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O53">
-    <cfRule type="containsText" dxfId="301" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="298" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77117,7 +79070,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P52">
-    <cfRule type="containsText" dxfId="300" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="297" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77134,7 +79087,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P55">
-    <cfRule type="containsText" dxfId="299" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="296" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77151,7 +79104,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O54">
-    <cfRule type="containsText" dxfId="298" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="295" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77168,7 +79121,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O49">
-    <cfRule type="containsText" dxfId="297" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="294" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77185,7 +79138,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R56">
-    <cfRule type="containsText" dxfId="296" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="293" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77202,7 +79155,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P57">
-    <cfRule type="containsText" dxfId="295" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="292" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77219,7 +79172,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O50">
-    <cfRule type="containsText" dxfId="294" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="291" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77236,7 +79189,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P49:P50">
-    <cfRule type="containsText" dxfId="293" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="290" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77253,7 +79206,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R51">
-    <cfRule type="containsText" dxfId="292" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="289" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77270,7 +79223,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R58">
-    <cfRule type="containsText" dxfId="291" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="288" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77287,7 +79240,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q55">
-    <cfRule type="containsText" dxfId="290" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="287" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77304,7 +79257,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O58">
-    <cfRule type="containsText" dxfId="289" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="286" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77321,7 +79274,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P58">
-    <cfRule type="containsText" dxfId="288" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="285" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77338,7 +79291,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q58">
-    <cfRule type="containsText" dxfId="287" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="284" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77355,7 +79308,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q53">
-    <cfRule type="containsText" dxfId="286" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="283" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77372,7 +79325,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="containsText" dxfId="285" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="282" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77389,7 +79342,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O59">
-    <cfRule type="containsText" dxfId="284" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="281" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77406,7 +79359,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P59">
-    <cfRule type="containsText" dxfId="283" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="280" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77423,7 +79376,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O60">
-    <cfRule type="containsText" dxfId="282" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="279" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77440,7 +79393,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q60">
-    <cfRule type="containsText" dxfId="281" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="278" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77457,7 +79410,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R60">
-    <cfRule type="containsText" dxfId="280" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="277" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77474,7 +79427,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61">
-    <cfRule type="containsText" dxfId="279" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="276" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77491,7 +79444,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P62">
-    <cfRule type="containsText" dxfId="278" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="275" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77508,7 +79461,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P64">
-    <cfRule type="containsText" dxfId="277" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="274" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77525,7 +79478,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P65">
-    <cfRule type="containsText" dxfId="276" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="273" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77542,7 +79495,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O63">
-    <cfRule type="containsText" dxfId="275" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="272" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77559,7 +79512,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q63">
-    <cfRule type="containsText" dxfId="274" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="271" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77576,7 +79529,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R63">
-    <cfRule type="containsText" dxfId="273" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="270" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77593,7 +79546,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O66:R66 O67:P67 R67">
-    <cfRule type="containsText" dxfId="272" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="269" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77610,7 +79563,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O68">
-    <cfRule type="containsText" dxfId="271" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="268" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77627,7 +79580,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O69:R69">
-    <cfRule type="containsText" dxfId="270" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="267" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77644,7 +79597,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O70:R70">
-    <cfRule type="containsText" dxfId="269" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="266" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77661,7 +79614,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70">
-    <cfRule type="containsText" dxfId="268" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="265" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77678,7 +79631,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O71:R71">
-    <cfRule type="containsText" dxfId="267" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="264" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77695,7 +79648,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V72">
-    <cfRule type="containsText" dxfId="266" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="263" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77712,7 +79665,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U71">
-    <cfRule type="containsText" dxfId="265" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="262" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77729,7 +79682,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V73">
-    <cfRule type="containsText" dxfId="264" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="261" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77746,7 +79699,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V71">
-    <cfRule type="containsText" dxfId="263" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="260" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77763,7 +79716,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O72:R72">
-    <cfRule type="containsText" dxfId="262" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="259" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77780,7 +79733,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U72">
-    <cfRule type="containsText" dxfId="261" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="258" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77797,7 +79750,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O73:R73">
-    <cfRule type="containsText" dxfId="260" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="257" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77814,7 +79767,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U73">
-    <cfRule type="containsText" dxfId="259" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="256" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77831,7 +79784,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O75">
-    <cfRule type="containsText" dxfId="258" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="255" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77848,7 +79801,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O76">
-    <cfRule type="containsText" dxfId="257" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="254" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77865,7 +79818,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V74">
-    <cfRule type="containsText" dxfId="256" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="253" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77882,7 +79835,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P74:R74">
-    <cfRule type="containsText" dxfId="255" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="252" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77899,7 +79852,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O78:R78 P80 O82 R80 R82">
-    <cfRule type="containsText" dxfId="254" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="251" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77916,7 +79869,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O77:R77">
-    <cfRule type="containsText" dxfId="253" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="250" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77933,7 +79886,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O83:R83 O85:R85 O87 Q87:R87">
-    <cfRule type="containsText" dxfId="252" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="249" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77950,12 +79903,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O79:R79 O81:R81">
-    <cfRule type="containsText" dxfId="251" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="248" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O84:R84 O86:R86">
-    <cfRule type="containsText" dxfId="250" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="247" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77972,7 +79925,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O88:R88 O90:R90 O92:R92 O94:R94 O96:R96">
-    <cfRule type="containsText" dxfId="249" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="246" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77989,7 +79942,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O89:R89 O91:R91 O93:R93 O95:R95">
-    <cfRule type="containsText" dxfId="248" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="245" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Collections/India/#Republic_of_India#Regular#[1957-present]#circulation_quality.xlsx
+++ b/Collections/India/#Republic_of_India#Regular#[1957-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\India\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C2A210-6696-48B2-B74D-FEA9AFF0B29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A60973-5730-435C-9548-8F030CABD5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1 Paisa" sheetId="28" r:id="rId1"/>
@@ -3712,6 +3712,15 @@
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="794">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -10040,15 +10049,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -10077,9 +10077,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="793"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="792" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="791"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -13294,7 +13294,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="I3 I5 I7 I9 I11 I19">
+  <conditionalFormatting sqref="I5 I3 I7 I9 I11 I19">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13307,11 +13307,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3 I5 I7 I9 I11 I19">
-    <cfRule type="containsText" dxfId="790" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="793" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6 K8 K10">
+  <conditionalFormatting sqref="K8 K6 K10">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13323,7 +13323,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4 J6 J8 J10 J21">
+  <conditionalFormatting sqref="J6 J4 J8 J10 J21">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13419,7 +13419,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3 J5 J7 J9 J11">
+  <conditionalFormatting sqref="J5 J3 J7 J9 J11">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13432,11 +13432,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3 J5 J7 J9 J11">
-    <cfRule type="containsText" dxfId="789" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="792" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3 K5 K7 K9 K11">
+  <conditionalFormatting sqref="K5 K3 K7 K9 K11">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13449,11 +13449,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3 K5 K7 K9 K11">
-    <cfRule type="containsText" dxfId="788" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="791" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4 I6 I8 I10 I21">
+  <conditionalFormatting sqref="I6 I4 I8 I10 I21">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13466,7 +13466,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4 I6 I8 I10 I21">
-    <cfRule type="containsText" dxfId="787" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="790" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13483,7 +13483,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6 J8 J10 J21">
-    <cfRule type="containsText" dxfId="786" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="789" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13500,7 +13500,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6 K8 K10">
-    <cfRule type="containsText" dxfId="785" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="788" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13517,7 +13517,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="784" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="787" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13534,52 +13534,52 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="783" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="786" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="782" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="785" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="781" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="784" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="780" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="783" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="779" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="782" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="778" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="781" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="777" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="780" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="776" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="779" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="775" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="778" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="774" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="777" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13596,7 +13596,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="containsText" dxfId="773" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="776" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13613,7 +13613,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="772" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="775" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20651,7 +20651,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q44 Q53 Q67 Q70 Q47">
+  <conditionalFormatting sqref="Q53 Q44 Q67 Q70 Q47">
     <cfRule type="colorScale" priority="328">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -20687,7 +20687,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P42 P54 P69 P72">
+  <conditionalFormatting sqref="P54 P42 P69 P72">
     <cfRule type="colorScale" priority="336">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -20747,7 +20747,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O44 O47 O53">
+  <conditionalFormatting sqref="O47 O44 O53">
     <cfRule type="colorScale" priority="326">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -20760,7 +20760,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P38">
-    <cfRule type="containsText" dxfId="244" priority="343" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="247" priority="343" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20777,7 +20777,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q38:Q39">
-    <cfRule type="containsText" dxfId="243" priority="341" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="246" priority="341" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20805,7 +20805,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q42 Q45 Q50 Q64 Q69 Q72">
+  <conditionalFormatting sqref="Q45 Q42 Q50 Q64 Q69 Q72">
     <cfRule type="colorScale" priority="334">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -20817,7 +20817,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O42 O45 O50 O69 O72">
+  <conditionalFormatting sqref="O45 O42 O50 O69 O72">
     <cfRule type="colorScale" priority="332">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -20829,7 +20829,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P44 P47 P67">
+  <conditionalFormatting sqref="P47 P44 P67">
     <cfRule type="colorScale" priority="330">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -20841,7 +20841,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R42 R45 R69">
+  <conditionalFormatting sqref="R45 R42 R69">
     <cfRule type="colorScale" priority="316">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -20890,7 +20890,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P29">
-    <cfRule type="containsText" dxfId="242" priority="347" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="245" priority="347" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20907,7 +20907,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q29">
-    <cfRule type="containsText" dxfId="241" priority="345" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="244" priority="345" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20924,7 +20924,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P46">
-    <cfRule type="containsText" dxfId="240" priority="309" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="243" priority="309" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20941,7 +20941,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q46">
-    <cfRule type="containsText" dxfId="239" priority="307" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="242" priority="307" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20958,7 +20958,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O38">
-    <cfRule type="containsText" dxfId="238" priority="339" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="241" priority="339" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20975,7 +20975,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O40">
-    <cfRule type="containsText" dxfId="237" priority="337" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="240" priority="337" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20992,7 +20992,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42 P54 P69 P72">
-    <cfRule type="containsText" dxfId="236" priority="335" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="239" priority="335" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21009,7 +21009,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q42 Q45 Q50 Q64 Q69 Q72">
-    <cfRule type="containsText" dxfId="235" priority="333" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="238" priority="333" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21026,7 +21026,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O42 O45 O50 O69 O72">
-    <cfRule type="containsText" dxfId="234" priority="331" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="237" priority="331" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21043,7 +21043,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P44 P47 P67">
-    <cfRule type="containsText" dxfId="233" priority="329" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="236" priority="329" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21060,7 +21060,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44 Q53 Q67 Q70 Q47">
-    <cfRule type="containsText" dxfId="232" priority="327" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="235" priority="327" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21077,7 +21077,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O44 O47 O53">
-    <cfRule type="containsText" dxfId="231" priority="325" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="234" priority="325" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21118,17 +21118,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P43">
-    <cfRule type="containsText" dxfId="230" priority="323" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="233" priority="323" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="containsText" dxfId="229" priority="313" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="232" priority="313" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R51">
-    <cfRule type="containsText" dxfId="228" priority="277" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="231" priority="277" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21145,7 +21145,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R46">
-    <cfRule type="containsText" dxfId="227" priority="303" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="230" priority="303" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21162,7 +21162,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R42 R45 R69">
-    <cfRule type="containsText" dxfId="226" priority="315" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="229" priority="315" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21179,7 +21179,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R48">
-    <cfRule type="containsText" dxfId="225" priority="295" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="228" priority="295" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21196,7 +21196,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S58">
-    <cfRule type="containsText" dxfId="224" priority="221" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="227" priority="221" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21237,17 +21237,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P76">
-    <cfRule type="containsText" dxfId="223" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="226" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O62">
-    <cfRule type="containsText" dxfId="222" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="225" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O46">
-    <cfRule type="containsText" dxfId="221" priority="305" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="224" priority="305" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21264,7 +21264,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q60">
-    <cfRule type="containsText" dxfId="220" priority="203" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="223" priority="203" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21317,22 +21317,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P48">
-    <cfRule type="containsText" dxfId="219" priority="301" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="222" priority="301" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R58">
-    <cfRule type="containsText" dxfId="218" priority="235" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="221" priority="235" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O48">
-    <cfRule type="containsText" dxfId="217" priority="297" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="220" priority="297" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O51">
-    <cfRule type="containsText" dxfId="216" priority="279" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="219" priority="279" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21385,22 +21385,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P52">
-    <cfRule type="containsText" dxfId="215" priority="275" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="218" priority="275" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R62">
-    <cfRule type="containsText" dxfId="214" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="217" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O52">
-    <cfRule type="containsText" dxfId="213" priority="271" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="216" priority="271" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T62">
-    <cfRule type="containsText" dxfId="212" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="215" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21417,7 +21417,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P49">
-    <cfRule type="containsText" dxfId="211" priority="285" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="214" priority="285" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21470,17 +21470,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P51">
-    <cfRule type="containsText" dxfId="210" priority="283" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="213" priority="283" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O55">
-    <cfRule type="containsText" dxfId="209" priority="263" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="212" priority="263" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65">
-    <cfRule type="containsText" dxfId="208" priority="185" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="211" priority="185" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21533,22 +21533,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P68">
-    <cfRule type="containsText" dxfId="207" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="210" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R65">
-    <cfRule type="containsText" dxfId="206" priority="181" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="209" priority="181" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R61">
-    <cfRule type="containsText" dxfId="205" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="208" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V65">
-    <cfRule type="containsText" dxfId="204" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="207" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21601,22 +21601,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P55">
-    <cfRule type="containsText" dxfId="203" priority="267" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="206" priority="267" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80">
-    <cfRule type="containsText" dxfId="202" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="205" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64">
-    <cfRule type="containsText" dxfId="201" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="204" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q79">
-    <cfRule type="containsText" dxfId="200" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="203" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21669,17 +21669,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q56">
-    <cfRule type="containsText" dxfId="199" priority="257" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="202" priority="257" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O71">
-    <cfRule type="containsText" dxfId="198" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="201" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U58">
-    <cfRule type="containsText" dxfId="197" priority="223" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="200" priority="223" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21696,7 +21696,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S55">
-    <cfRule type="containsText" dxfId="196" priority="251" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="199" priority="251" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21737,7 +21737,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O80">
-    <cfRule type="containsText" dxfId="195" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="198" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21754,32 +21754,32 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R57">
-    <cfRule type="containsText" dxfId="194" priority="243" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="197" priority="243" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P59">
-    <cfRule type="containsText" dxfId="193" priority="225" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="196" priority="225" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R81">
-    <cfRule type="containsText" dxfId="192" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="195" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R68">
-    <cfRule type="containsText" dxfId="191" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="194" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q74">
-    <cfRule type="containsText" dxfId="190" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="193" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q82">
-    <cfRule type="containsText" dxfId="189" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="192" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21820,22 +21820,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O58">
-    <cfRule type="containsText" dxfId="188" priority="237" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="191" priority="237" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O79">
-    <cfRule type="containsText" dxfId="187" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="190" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P58">
-    <cfRule type="containsText" dxfId="186" priority="241" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="189" priority="241" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O65">
-    <cfRule type="containsText" dxfId="185" priority="183" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="188" priority="183" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21876,22 +21876,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q78">
-    <cfRule type="containsText" dxfId="184" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="187" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R84">
-    <cfRule type="containsText" dxfId="183" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="186" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P79">
-    <cfRule type="containsText" dxfId="182" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="185" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="containsText" dxfId="181" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="184" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21908,12 +21908,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80">
-    <cfRule type="containsText" dxfId="180" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="183" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q63">
-    <cfRule type="containsText" dxfId="179" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="182" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21930,7 +21930,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P86 P88 P90 P92">
-    <cfRule type="containsText" dxfId="178" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="181" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21946,7 +21946,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O85 O87 O89 O91 O93">
+  <conditionalFormatting sqref="O87 O85 O89 O91 O93">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -21971,17 +21971,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q85 Q87 Q89 Q91 Q93">
-    <cfRule type="containsText" dxfId="177" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="180" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O85 O87 O89 O91 O93">
-    <cfRule type="containsText" dxfId="176" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="179" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q62">
-    <cfRule type="containsText" dxfId="175" priority="199" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="178" priority="199" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22022,17 +22022,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80">
-    <cfRule type="containsText" dxfId="174" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="177" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R78">
-    <cfRule type="containsText" dxfId="173" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="176" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O68">
-    <cfRule type="containsText" dxfId="172" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="175" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22061,22 +22061,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q71">
-    <cfRule type="containsText" dxfId="171" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="174" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q75">
-    <cfRule type="containsText" dxfId="170" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="173" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O78">
-    <cfRule type="containsText" dxfId="169" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="172" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P62">
-    <cfRule type="containsText" dxfId="168" priority="201" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="171" priority="201" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22093,12 +22093,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q81">
-    <cfRule type="containsText" dxfId="167" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="170" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q73">
-    <cfRule type="containsText" dxfId="166" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="169" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22114,7 +22114,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q85 Q87 Q89 Q91 Q93">
+  <conditionalFormatting sqref="Q87 Q85 Q89 Q91 Q93">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -22127,17 +22127,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P65">
-    <cfRule type="containsText" dxfId="165" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="168" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O82">
-    <cfRule type="containsText" dxfId="164" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="167" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R82">
-    <cfRule type="containsText" dxfId="163" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="166" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22165,7 +22165,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O86 O88 O90 O92">
+  <conditionalFormatting sqref="O88 O86 O90 O92">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -22178,26 +22178,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O75">
-    <cfRule type="containsText" dxfId="162" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="165" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q84">
-    <cfRule type="containsText" dxfId="161" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="164" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O86 O88 O90 O92">
-    <cfRule type="containsText" dxfId="160" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="163" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q66">
-    <cfRule type="containsText" dxfId="159" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="162" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q86 Q88 Q90 Q92">
+  <conditionalFormatting sqref="Q88 Q86 Q90 Q92">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -22209,7 +22209,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P86 P88 P90 P92">
+  <conditionalFormatting sqref="P88 P86 P90 P92">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -22222,31 +22222,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O84">
-    <cfRule type="containsText" dxfId="158" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="161" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P71">
-    <cfRule type="containsText" dxfId="157" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="160" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O81">
-    <cfRule type="containsText" dxfId="156" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="159" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R71">
-    <cfRule type="containsText" dxfId="155" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="158" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P82">
-    <cfRule type="containsText" dxfId="154" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="157" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R85 R87 R89 R91 R93">
+  <conditionalFormatting sqref="R87 R85 R89 R91 R93">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -22258,7 +22258,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P85 P87 P89 P91 P93">
+  <conditionalFormatting sqref="P87 P85 P89 P91 P93">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -22271,26 +22271,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O83">
-    <cfRule type="containsText" dxfId="153" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="156" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R86 R88 R90">
-    <cfRule type="containsText" dxfId="152" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="155" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R85 R87 R89 R91 R93">
-    <cfRule type="containsText" dxfId="151" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="154" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83">
-    <cfRule type="containsText" dxfId="150" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="153" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R86 R88 R90">
+  <conditionalFormatting sqref="R88 R86 R90">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -22303,27 +22303,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P85 P87 P89 P91 P93">
-    <cfRule type="containsText" dxfId="149" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="152" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83">
-    <cfRule type="containsText" dxfId="148" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="151" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q86 Q88 Q90 Q92">
-    <cfRule type="containsText" dxfId="147" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="150" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P77">
-    <cfRule type="containsText" dxfId="146" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="149" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P81">
-    <cfRule type="containsText" dxfId="145" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="148" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22340,7 +22340,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O94">
-    <cfRule type="containsText" dxfId="144" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="147" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22369,12 +22369,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R94">
-    <cfRule type="containsText" dxfId="143" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="146" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P94">
-    <cfRule type="containsText" dxfId="142" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="145" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22391,12 +22391,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q96">
-    <cfRule type="containsText" dxfId="141" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="144" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O96">
-    <cfRule type="containsText" dxfId="140" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="143" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22437,12 +22437,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R96">
-    <cfRule type="containsText" dxfId="139" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="142" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P96">
-    <cfRule type="containsText" dxfId="138" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="141" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22459,7 +22459,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O95">
-    <cfRule type="containsText" dxfId="137" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="140" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22488,12 +22488,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R95">
-    <cfRule type="containsText" dxfId="136" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="139" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P95">
-    <cfRule type="containsText" dxfId="135" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="138" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27492,7 +27492,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M38 M42 M46 M50 M55">
+  <conditionalFormatting sqref="M42 M38 M46 M50 M55">
     <cfRule type="colorScale" priority="308">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27504,7 +27504,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K38 K42 K46 K50 K55">
+  <conditionalFormatting sqref="K42 K38 K46 K50 K55">
     <cfRule type="colorScale" priority="312">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27552,7 +27552,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L38 L42 L46 L50 L55">
+  <conditionalFormatting sqref="L42 L38 L46 L50 L55">
     <cfRule type="colorScale" priority="310">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27589,7 +27589,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63">
-    <cfRule type="containsText" dxfId="134" priority="223" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="137" priority="223" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27606,56 +27606,56 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L63">
-    <cfRule type="containsText" dxfId="133" priority="221" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="136" priority="221" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L38 L42 L46 L50 L55">
-    <cfRule type="containsText" dxfId="132" priority="309" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="135" priority="309" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M38 M42 M46 M50 M55">
-    <cfRule type="containsText" dxfId="131" priority="307" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="134" priority="307" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M63">
-    <cfRule type="containsText" dxfId="130" priority="219" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="133" priority="219" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N45">
-    <cfRule type="containsText" dxfId="129" priority="217" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="132" priority="217" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47">
-    <cfRule type="containsText" dxfId="128" priority="215" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="131" priority="215" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38 K42 K46 K50 K55">
-    <cfRule type="containsText" dxfId="127" priority="311" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="130" priority="311" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47">
-    <cfRule type="containsText" dxfId="126" priority="211" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="129" priority="211" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47">
-    <cfRule type="containsText" dxfId="125" priority="209" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="128" priority="209" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L47">
-    <cfRule type="containsText" dxfId="124" priority="213" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="127" priority="213" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L40 L44 L52">
+  <conditionalFormatting sqref="L44 L40 L52">
     <cfRule type="colorScale" priority="304">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27668,11 +27668,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40 L44 L52">
-    <cfRule type="containsText" dxfId="123" priority="303" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="126" priority="303" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K40 K44 K52 K57">
+  <conditionalFormatting sqref="K44 K40 K52 K57">
     <cfRule type="colorScale" priority="306">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27685,7 +27685,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40 K44 K52 K57">
-    <cfRule type="containsText" dxfId="122" priority="305" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="125" priority="305" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27713,7 +27713,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M44 M52 M57 M61">
+  <conditionalFormatting sqref="M52 M44 M57 M61">
     <cfRule type="colorScale" priority="302">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27726,17 +27726,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49">
-    <cfRule type="containsText" dxfId="121" priority="207" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="124" priority="207" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49">
-    <cfRule type="containsText" dxfId="120" priority="205" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="123" priority="205" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M44 M52 M57 M61">
-    <cfRule type="containsText" dxfId="119" priority="301" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="122" priority="301" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27777,17 +27777,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K48">
-    <cfRule type="containsText" dxfId="118" priority="299" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="121" priority="299" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L48">
-    <cfRule type="containsText" dxfId="117" priority="297" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="120" priority="297" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49">
-    <cfRule type="containsText" dxfId="116" priority="203" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="119" priority="203" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27816,12 +27816,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N49">
-    <cfRule type="containsText" dxfId="115" priority="201" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="118" priority="201" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K51">
-    <cfRule type="containsText" dxfId="114" priority="199" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="117" priority="199" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27838,7 +27838,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50">
-    <cfRule type="containsText" dxfId="113" priority="295" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="116" priority="295" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27855,7 +27855,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K59">
-    <cfRule type="containsText" dxfId="112" priority="293" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="115" priority="293" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27872,7 +27872,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59">
-    <cfRule type="containsText" dxfId="111" priority="291" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="114" priority="291" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27913,17 +27913,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L39">
-    <cfRule type="containsText" dxfId="110" priority="287" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="113" priority="287" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M39">
-    <cfRule type="containsText" dxfId="109" priority="285" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="112" priority="285" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="containsText" dxfId="108" priority="289" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="111" priority="289" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27964,17 +27964,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L41">
-    <cfRule type="containsText" dxfId="107" priority="281" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="110" priority="281" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M41">
-    <cfRule type="containsText" dxfId="106" priority="279" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="109" priority="279" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="containsText" dxfId="105" priority="283" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="108" priority="283" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28015,17 +28015,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L43">
-    <cfRule type="containsText" dxfId="104" priority="275" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="107" priority="275" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M43">
-    <cfRule type="containsText" dxfId="103" priority="273" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="106" priority="273" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="containsText" dxfId="102" priority="277" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="105" priority="277" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28066,17 +28066,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="containsText" dxfId="101" priority="269" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="104" priority="269" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M45">
-    <cfRule type="containsText" dxfId="100" priority="267" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="103" priority="267" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K45">
-    <cfRule type="containsText" dxfId="99" priority="271" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="102" priority="271" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28117,17 +28117,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60">
-    <cfRule type="containsText" dxfId="98" priority="225" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="101" priority="225" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N53">
-    <cfRule type="containsText" dxfId="97" priority="185" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="100" priority="185" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L60">
-    <cfRule type="containsText" dxfId="96" priority="227" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="99" priority="227" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28168,17 +28168,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58">
-    <cfRule type="containsText" dxfId="95" priority="235" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="98" priority="235" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L58">
-    <cfRule type="containsText" dxfId="94" priority="233" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="97" priority="233" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M53">
-    <cfRule type="containsText" dxfId="93" priority="243" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="96" priority="243" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28219,17 +28219,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K56">
-    <cfRule type="containsText" dxfId="92" priority="181" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="95" priority="181" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L56">
-    <cfRule type="containsText" dxfId="91" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="94" priority="179" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L53">
-    <cfRule type="containsText" dxfId="90" priority="245" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="93" priority="245" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28270,17 +28270,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O53">
-    <cfRule type="containsText" dxfId="89" priority="183" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="92" priority="183" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L68">
-    <cfRule type="containsText" dxfId="88" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="91" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K53">
-    <cfRule type="containsText" dxfId="87" priority="247" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="90" priority="247" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28321,17 +28321,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M56">
-    <cfRule type="containsText" dxfId="86" priority="177" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="89" priority="177" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M58">
-    <cfRule type="containsText" dxfId="85" priority="231" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="88" priority="231" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M68">
-    <cfRule type="containsText" dxfId="84" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="87" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28372,17 +28372,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="containsText" dxfId="83" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="86" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N56">
-    <cfRule type="containsText" dxfId="82" priority="175" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="85" priority="175" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K75">
-    <cfRule type="containsText" dxfId="81" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="84" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28423,17 +28423,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67">
-    <cfRule type="containsText" dxfId="80" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="83" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67">
-    <cfRule type="containsText" dxfId="79" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="82" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M66">
-    <cfRule type="containsText" dxfId="78" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="81" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28474,17 +28474,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L51">
-    <cfRule type="containsText" dxfId="77" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="80" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M51">
-    <cfRule type="containsText" dxfId="76" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="79" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M67">
-    <cfRule type="containsText" dxfId="75" priority="149" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="149" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28501,7 +28501,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N51">
-    <cfRule type="containsText" dxfId="74" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28542,17 +28542,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M69">
-    <cfRule type="containsText" dxfId="73" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L77">
-    <cfRule type="containsText" dxfId="72" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="75" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K68">
-    <cfRule type="containsText" dxfId="71" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="74" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28569,7 +28569,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N62">
-    <cfRule type="containsText" dxfId="70" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="73" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28598,12 +28598,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M75">
-    <cfRule type="containsText" dxfId="69" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="72" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K71">
-    <cfRule type="containsText" dxfId="68" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28620,11 +28620,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L76">
-    <cfRule type="containsText" dxfId="67" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="70" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M80 M84 M86 M89">
+  <conditionalFormatting sqref="M84 M80 M86 M89">
     <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28661,21 +28661,21 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O56">
-    <cfRule type="containsText" dxfId="66" priority="173" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="173" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M80 M84 M86 M89">
-    <cfRule type="containsText" dxfId="65" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="68" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K73">
-    <cfRule type="containsText" dxfId="64" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N80 N84 N86 N89">
+  <conditionalFormatting sqref="N84 N80 N86 N89">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28688,7 +28688,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N80 N84 N86 N89">
-    <cfRule type="containsText" dxfId="63" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28705,17 +28705,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N60">
-    <cfRule type="containsText" dxfId="62" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N58">
-    <cfRule type="containsText" dxfId="61" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="64" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L74">
-    <cfRule type="containsText" dxfId="60" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="63" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28732,12 +28732,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N75">
-    <cfRule type="containsText" dxfId="59" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="62" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M79">
-    <cfRule type="containsText" dxfId="58" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="61" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28754,7 +28754,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M62">
-    <cfRule type="containsText" dxfId="57" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28771,11 +28771,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L62">
-    <cfRule type="containsText" dxfId="56" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="59" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K78 K82 K85 K87 K90">
+  <conditionalFormatting sqref="K82 K78 K85 K87 K90">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28788,11 +28788,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K62">
-    <cfRule type="containsText" dxfId="55" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="58" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L80 L84 L86 L89">
+  <conditionalFormatting sqref="L84 L80 L86 L89">
     <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28804,7 +28804,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N78 N82 N85 N87 N90">
+  <conditionalFormatting sqref="N82 N78 N85 N87 N90">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28816,7 +28816,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M78 M82 M85 M87">
+  <conditionalFormatting sqref="M82 M78 M85 M87">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28829,16 +28829,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L80 L84 L86 L89">
-    <cfRule type="containsText" dxfId="54" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="57" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78 K82 K85 K87 K90">
-    <cfRule type="containsText" dxfId="53" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L78 L82 L85 L87 L90">
+  <conditionalFormatting sqref="L82 L78 L85 L87 L90">
     <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28851,12 +28851,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M78 M82 M85 M87">
-    <cfRule type="containsText" dxfId="52" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="55" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N78 N82 N85 N87 N90">
-    <cfRule type="containsText" dxfId="51" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="54" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28873,11 +28873,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M70">
-    <cfRule type="containsText" dxfId="50" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="53" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K80 K84 K86 K89">
+  <conditionalFormatting sqref="K84 K80 K86 K89">
     <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -28890,12 +28890,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M81">
-    <cfRule type="containsText" dxfId="49" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="52" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K72">
-    <cfRule type="containsText" dxfId="48" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28912,12 +28912,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80 K84 K86 K89">
-    <cfRule type="containsText" dxfId="47" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="50" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L78 L82 L85 L87 L90">
-    <cfRule type="containsText" dxfId="46" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28958,22 +28958,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M88">
-    <cfRule type="containsText" dxfId="45" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N93">
-    <cfRule type="containsText" dxfId="44" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K92">
-    <cfRule type="containsText" dxfId="43" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83">
-    <cfRule type="containsText" dxfId="42" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28990,7 +28990,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M92">
-    <cfRule type="containsText" dxfId="41" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="44" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29007,7 +29007,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L92">
-    <cfRule type="containsText" dxfId="40" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29024,7 +29024,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93">
-    <cfRule type="containsText" dxfId="39" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29041,12 +29041,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N92">
-    <cfRule type="containsText" dxfId="38" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="41" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N88">
-    <cfRule type="containsText" dxfId="37" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29063,7 +29063,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L93">
-    <cfRule type="containsText" dxfId="36" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29092,7 +29092,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L94">
-    <cfRule type="containsText" dxfId="35" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29109,7 +29109,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K91">
-    <cfRule type="containsText" dxfId="34" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29126,7 +29126,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L91">
-    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29143,7 +29143,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M93">
-    <cfRule type="containsText" dxfId="32" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29160,12 +29160,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M94">
-    <cfRule type="containsText" dxfId="31" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N91">
-    <cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29194,7 +29194,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M91">
-    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32412,7 +32412,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J57 J59 J61 J63 J65 J67 J69">
+  <conditionalFormatting sqref="J59 J57 J61 J63 J65 J67 J69">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32496,7 +32496,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K59 K57 K61 K63 K65 K67">
+  <conditionalFormatting sqref="K57 K59 K61 K63 K65 K67">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32568,7 +32568,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M59 M57 M61 M63 M65 M67 M69">
+  <conditionalFormatting sqref="M57 M59 M61 M63 M65 M67 M69">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32581,11 +32581,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L54">
-    <cfRule type="containsText" dxfId="28" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L59 L57 L61 L63 L65 L67 L69">
+  <conditionalFormatting sqref="L57 L59 L61 L63 L65 L67 L69">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32598,56 +32598,56 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K54">
-    <cfRule type="containsText" dxfId="27" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L57 L59 L61 L63 L65 L67 L69">
-    <cfRule type="containsText" dxfId="26" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K57 K59 K61 K63 K65 K67">
-    <cfRule type="containsText" dxfId="25" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M55">
-    <cfRule type="containsText" dxfId="24" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L55">
-    <cfRule type="containsText" dxfId="23" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55">
-    <cfRule type="containsText" dxfId="22" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M56">
-    <cfRule type="containsText" dxfId="21" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L56">
-    <cfRule type="containsText" dxfId="20" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K56">
-    <cfRule type="containsText" dxfId="19" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M57 M59 M61 M63 M65 M67 M69">
-    <cfRule type="containsText" dxfId="18" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M58 M60 M62 M64 M66 M68">
+  <conditionalFormatting sqref="M60 M58 M62 M64 M66 M68">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32659,7 +32659,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L58 L60 L62 L64 L66 L68">
+  <conditionalFormatting sqref="L60 L58 L62 L64 L66 L68">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32671,7 +32671,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K58 K60 K62 K64 K66 K68">
+  <conditionalFormatting sqref="K60 K58 K62 K64 K66 K68">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32684,41 +32684,41 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M58 M60 M62 M64 M66 M68">
-    <cfRule type="containsText" dxfId="17" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L58 L60 L62 L64 L66 L68">
-    <cfRule type="containsText" dxfId="16" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58 K60 K62 K64 K66 K68">
-    <cfRule type="containsText" dxfId="15" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M51">
-    <cfRule type="containsText" dxfId="14" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M52">
-    <cfRule type="containsText" dxfId="13" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M53">
-    <cfRule type="containsText" dxfId="12" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M54">
-    <cfRule type="containsText" dxfId="11" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J58 J60 J62 J64 J66 J68">
+  <conditionalFormatting sqref="J60 J58 J62 J64 J66 J68">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -32731,12 +32731,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J58 J60 J62 J64 J66 J68">
-    <cfRule type="containsText" dxfId="10" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J57 J59 J61 J63 J65 J67 J69">
-    <cfRule type="containsText" dxfId="9" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35939,7 +35939,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M66 M68">
+  <conditionalFormatting sqref="M68 M66">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -35951,7 +35951,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L66 L68">
+  <conditionalFormatting sqref="L68 L66">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -35964,21 +35964,21 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L66 L68">
-    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K66">
-    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M66 M68">
-    <cfRule type="containsText" dxfId="6" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M65 M67">
+  <conditionalFormatting sqref="M67 M65">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -36002,7 +36002,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K65 K67">
+  <conditionalFormatting sqref="K67 K65">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -36015,21 +36015,21 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M65 M67">
-    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67">
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65 K67">
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J66 J68">
+  <conditionalFormatting sqref="J68 J66">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -36042,7 +36042,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J66 J68">
-    <cfRule type="containsText" dxfId="2" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36059,7 +36059,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36076,7 +36076,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K68">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39366,7 +39366,7 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="J3 J5 J7 J9 J11">
+  <conditionalFormatting sqref="J5 J3 J7 J9 J11">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -39379,11 +39379,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3 J5 J7 J9 J11">
-    <cfRule type="containsText" dxfId="771" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="774" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6 K8 K10">
+  <conditionalFormatting sqref="K8 K6 K10">
     <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -39395,7 +39395,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4 J6 J8 J10">
+  <conditionalFormatting sqref="J6 J4 J8 J10">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -39504,11 +39504,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="770" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="773" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3 K5 K7 K9 K11">
+  <conditionalFormatting sqref="K5 K3 K7 K9 K11">
     <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -39521,12 +39521,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3 K5 K7 K9 K11">
-    <cfRule type="containsText" dxfId="769" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="772" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6 K8 K10">
-    <cfRule type="containsText" dxfId="768" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="771" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39543,7 +39543,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6 J8 J10">
-    <cfRule type="containsText" dxfId="767" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="770" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39560,7 +39560,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="766" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="769" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39577,7 +39577,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13:J14">
-    <cfRule type="containsText" dxfId="765" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="768" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39594,47 +39594,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="764" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="767" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="763" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="766" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19">
-    <cfRule type="containsText" dxfId="762" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="765" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="761" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="764" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="760" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="763" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19">
-    <cfRule type="containsText" dxfId="759" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="762" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="758" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="761" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="757" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="760" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="containsText" dxfId="756" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="759" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39651,7 +39651,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23">
-    <cfRule type="containsText" dxfId="755" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="758" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39668,7 +39668,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="754" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="757" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39685,7 +39685,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21">
-    <cfRule type="containsText" dxfId="753" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="756" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39702,7 +39702,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="containsText" dxfId="752" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="755" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39719,7 +39719,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25">
-    <cfRule type="containsText" dxfId="751" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="754" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39736,7 +39736,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27">
-    <cfRule type="containsText" dxfId="750" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="753" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39753,7 +39753,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29">
-    <cfRule type="containsText" dxfId="749" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="752" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39770,7 +39770,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="containsText" dxfId="748" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="751" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39787,7 +39787,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I33">
-    <cfRule type="containsText" dxfId="747" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="750" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39804,7 +39804,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29">
-    <cfRule type="containsText" dxfId="746" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="749" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39821,7 +39821,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31">
-    <cfRule type="containsText" dxfId="745" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="748" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39838,7 +39838,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31">
-    <cfRule type="containsText" dxfId="744" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="747" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39855,7 +39855,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33:J34">
-    <cfRule type="containsText" dxfId="743" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="746" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39872,7 +39872,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I36">
-    <cfRule type="containsText" dxfId="742" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="745" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39889,7 +39889,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J36">
-    <cfRule type="containsText" dxfId="741" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="744" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39906,7 +39906,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38">
-    <cfRule type="containsText" dxfId="740" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="743" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42807,7 +42807,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="containsText" dxfId="739" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="742" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42920,7 +42920,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J10">
-    <cfRule type="containsText" dxfId="738" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="741" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42937,12 +42937,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10">
-    <cfRule type="containsText" dxfId="737" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="740" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="736" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="739" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42959,12 +42959,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="735" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="738" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="734" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="737" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42981,7 +42981,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="733" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="736" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42998,37 +42998,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="732" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="735" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="731" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="734" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="containsText" dxfId="730" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="733" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16">
-    <cfRule type="containsText" dxfId="729" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="732" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="containsText" dxfId="728" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="731" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="727" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="730" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17">
-    <cfRule type="containsText" dxfId="726" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="729" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43045,7 +43045,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19">
-    <cfRule type="containsText" dxfId="725" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="728" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43062,7 +43062,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19">
-    <cfRule type="containsText" dxfId="724" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="727" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43091,12 +43091,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11">
-    <cfRule type="containsText" dxfId="723" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="726" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="containsText" dxfId="722" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="725" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43113,7 +43113,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="721" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="724" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43154,17 +43154,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="720" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="723" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="719" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="722" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="718" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="721" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43193,12 +43193,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="717" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="720" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21">
-    <cfRule type="containsText" dxfId="716" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="719" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47124,7 +47124,7 @@
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="K7 K9 K12 K23">
+  <conditionalFormatting sqref="K9 K7 K12 K23">
     <cfRule type="colorScale" priority="210">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -47137,11 +47137,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7 K9 K12 K23">
-    <cfRule type="containsText" dxfId="715" priority="209" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="718" priority="209" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6 M8 M11">
+  <conditionalFormatting sqref="M8 M6 M11">
     <cfRule type="colorScale" priority="200">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -47153,7 +47153,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4 L6 L8 L11 L26">
+  <conditionalFormatting sqref="L6 L4 L8 L11 L26">
     <cfRule type="colorScale" priority="202">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -47237,7 +47237,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3 L5 L7 L9 L12">
+  <conditionalFormatting sqref="L5 L3 L7 L9 L12">
     <cfRule type="colorScale" priority="208">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -47250,11 +47250,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3 L5 L7 L9 L12">
-    <cfRule type="containsText" dxfId="714" priority="207" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="717" priority="207" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3 M5 M7 M9 M12">
+  <conditionalFormatting sqref="M5 M3 M7 M9 M12">
     <cfRule type="colorScale" priority="206">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -47267,11 +47267,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3 M5 M7 M9 M12">
-    <cfRule type="containsText" dxfId="713" priority="205" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="716" priority="205" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K11 K8 K26">
+  <conditionalFormatting sqref="K8 K11 K26">
     <cfRule type="colorScale" priority="204">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -47284,7 +47284,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8 K11 K26">
-    <cfRule type="containsText" dxfId="712" priority="203" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="715" priority="203" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47301,7 +47301,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4 L6 L8 L11 L26">
-    <cfRule type="containsText" dxfId="711" priority="201" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="714" priority="201" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47318,7 +47318,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6 M8 M11">
-    <cfRule type="containsText" dxfId="710" priority="199" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="713" priority="199" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47335,47 +47335,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13">
-    <cfRule type="containsText" dxfId="709" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="712" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21">
-    <cfRule type="containsText" dxfId="708" priority="175" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="711" priority="175" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21">
-    <cfRule type="containsText" dxfId="707" priority="173" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="710" priority="173" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14">
-    <cfRule type="containsText" dxfId="706" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="709" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L17">
-    <cfRule type="containsText" dxfId="705" priority="185" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="708" priority="185" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M14">
-    <cfRule type="containsText" dxfId="704" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="707" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="containsText" dxfId="703" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="706" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="containsText" dxfId="702" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="705" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M17">
-    <cfRule type="containsText" dxfId="701" priority="183" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="704" priority="183" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47392,7 +47392,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10">
-    <cfRule type="containsText" dxfId="700" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="703" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47409,7 +47409,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="699" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="702" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47426,7 +47426,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13">
-    <cfRule type="containsText" dxfId="698" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="701" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47455,12 +47455,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M15">
-    <cfRule type="containsText" dxfId="697" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="700" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16">
-    <cfRule type="containsText" dxfId="696" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="699" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47501,17 +47501,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="695" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="698" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24">
-    <cfRule type="containsText" dxfId="694" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="697" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18">
-    <cfRule type="containsText" dxfId="693" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="696" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47528,7 +47528,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L15">
-    <cfRule type="containsText" dxfId="692" priority="149" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="695" priority="149" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47569,17 +47569,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18">
-    <cfRule type="containsText" dxfId="691" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="694" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19">
-    <cfRule type="containsText" dxfId="690" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="693" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18">
-    <cfRule type="containsText" dxfId="689" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="692" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47608,12 +47608,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="containsText" dxfId="688" priority="117" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="691" priority="117" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="containsText" dxfId="687" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="690" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47630,7 +47630,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23">
-    <cfRule type="containsText" dxfId="686" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="689" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47647,7 +47647,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21">
-    <cfRule type="containsText" dxfId="685" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="688" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47664,7 +47664,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L29">
-    <cfRule type="containsText" dxfId="684" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="687" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47681,7 +47681,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29">
-    <cfRule type="containsText" dxfId="683" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="686" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47710,12 +47710,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="682" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="685" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="containsText" dxfId="681" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="684" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47732,7 +47732,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="containsText" dxfId="680" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="683" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47761,12 +47761,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L32">
-    <cfRule type="containsText" dxfId="679" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="682" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L36">
-    <cfRule type="containsText" dxfId="678" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="681" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47795,12 +47795,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M36">
-    <cfRule type="containsText" dxfId="677" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="680" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M29">
-    <cfRule type="containsText" dxfId="676" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="679" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47817,7 +47817,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M34">
-    <cfRule type="containsText" dxfId="675" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="678" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47846,12 +47846,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="containsText" dxfId="674" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="677" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L38">
-    <cfRule type="containsText" dxfId="673" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="676" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47868,7 +47868,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32">
-    <cfRule type="containsText" dxfId="672" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="675" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47897,12 +47897,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36">
-    <cfRule type="containsText" dxfId="671" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="674" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L34">
-    <cfRule type="containsText" dxfId="670" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="673" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47919,7 +47919,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="containsText" dxfId="669" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="672" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47936,7 +47936,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37">
-    <cfRule type="containsText" dxfId="668" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="671" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47965,12 +47965,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="containsText" dxfId="667" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="670" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L37">
-    <cfRule type="containsText" dxfId="666" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="669" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47987,7 +47987,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M42">
-    <cfRule type="containsText" dxfId="665" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="668" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48016,12 +48016,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="containsText" dxfId="664" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="667" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L41">
-    <cfRule type="containsText" dxfId="663" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="666" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48038,7 +48038,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M39">
-    <cfRule type="containsText" dxfId="662" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="665" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48055,7 +48055,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40">
-    <cfRule type="containsText" dxfId="661" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="664" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48072,7 +48072,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L42">
-    <cfRule type="containsText" dxfId="660" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="663" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48089,7 +48089,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M41">
-    <cfRule type="containsText" dxfId="659" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="662" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48106,7 +48106,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L44">
-    <cfRule type="containsText" dxfId="658" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="661" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48123,7 +48123,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="containsText" dxfId="657" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="660" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48140,7 +48140,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K51">
-    <cfRule type="containsText" dxfId="656" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="659" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48157,7 +48157,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44">
-    <cfRule type="containsText" dxfId="655" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="658" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48174,7 +48174,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M44">
-    <cfRule type="containsText" dxfId="654" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="657" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48191,7 +48191,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L46">
-    <cfRule type="containsText" dxfId="653" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="656" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48208,7 +48208,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K46">
-    <cfRule type="containsText" dxfId="652" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="655" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48225,7 +48225,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M46">
-    <cfRule type="containsText" dxfId="651" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="654" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48242,7 +48242,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K48">
-    <cfRule type="containsText" dxfId="650" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="653" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48259,7 +48259,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49">
-    <cfRule type="containsText" dxfId="649" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="652" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48276,7 +48276,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49">
-    <cfRule type="containsText" dxfId="648" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="651" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48293,7 +48293,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M48">
-    <cfRule type="containsText" dxfId="647" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="650" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48310,7 +48310,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M50">
-    <cfRule type="containsText" dxfId="646" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="649" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48327,7 +48327,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L56">
-    <cfRule type="containsText" dxfId="645" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="648" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48344,7 +48344,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52">
-    <cfRule type="containsText" dxfId="644" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="647" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48361,11 +48361,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M52">
-    <cfRule type="containsText" dxfId="643" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="646" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K53 K55 K57 K59">
+  <conditionalFormatting sqref="K55 K53 K57 K59">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -48378,11 +48378,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K53 K55 K57 K59">
-    <cfRule type="containsText" dxfId="642" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="645" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M53 M55 M59">
+  <conditionalFormatting sqref="M55 M53 M59">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -48395,11 +48395,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M53 M55 M59">
-    <cfRule type="containsText" dxfId="641" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="644" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M54 M56 M58">
+  <conditionalFormatting sqref="M56 M54 M58">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -48412,7 +48412,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M54 M56 M58">
-    <cfRule type="containsText" dxfId="640" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="643" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48429,11 +48429,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L51">
-    <cfRule type="containsText" dxfId="639" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="642" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K54 K56 K58 K60">
+  <conditionalFormatting sqref="K56 K54 K58 K60">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -48446,7 +48446,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K54 K56 K58 K60">
-    <cfRule type="containsText" dxfId="638" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="641" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48463,7 +48463,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L57">
-    <cfRule type="containsText" dxfId="637" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="640" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53225,7 +53225,7 @@
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="G1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="L12 L9">
+  <conditionalFormatting sqref="L9 L12">
     <cfRule type="colorScale" priority="238">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -53238,7 +53238,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9 L12">
-    <cfRule type="containsText" dxfId="636" priority="237" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="639" priority="237" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53254,7 +53254,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6 M8 M10 M25">
+  <conditionalFormatting sqref="M8 M6 M10 M25">
     <cfRule type="colorScale" priority="230">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -53326,7 +53326,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3 M9 M12">
+  <conditionalFormatting sqref="M9 M3 M12">
     <cfRule type="colorScale" priority="236">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -53339,11 +53339,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3 M9 M12">
-    <cfRule type="containsText" dxfId="635" priority="235" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="638" priority="235" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3 N9 N12">
+  <conditionalFormatting sqref="N9 N3 N12">
     <cfRule type="colorScale" priority="234">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -53356,11 +53356,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3 N9 N12">
-    <cfRule type="containsText" dxfId="634" priority="233" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="637" priority="233" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L10 L8 L25">
+  <conditionalFormatting sqref="L8 L10 L25">
     <cfRule type="colorScale" priority="232">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -53373,7 +53373,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8 L10 L25">
-    <cfRule type="containsText" dxfId="633" priority="231" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="636" priority="231" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53390,7 +53390,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6 M8 M10 M25">
-    <cfRule type="containsText" dxfId="632" priority="229" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="635" priority="229" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53407,7 +53407,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="containsText" dxfId="631" priority="227" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="634" priority="227" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53424,7 +53424,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M15">
-    <cfRule type="containsText" dxfId="630" priority="219" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="633" priority="219" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53441,42 +53441,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N15">
-    <cfRule type="containsText" dxfId="629" priority="217" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="632" priority="217" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18">
-    <cfRule type="containsText" dxfId="628" priority="207" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="631" priority="207" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18">
-    <cfRule type="containsText" dxfId="627" priority="205" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="630" priority="205" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L15">
-    <cfRule type="containsText" dxfId="626" priority="221" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="629" priority="221" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L16">
-    <cfRule type="containsText" dxfId="625" priority="215" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="628" priority="215" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16">
-    <cfRule type="containsText" dxfId="624" priority="213" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="627" priority="213" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16">
-    <cfRule type="containsText" dxfId="623" priority="211" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="626" priority="211" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18">
-    <cfRule type="containsText" dxfId="622" priority="209" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="625" priority="209" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53493,7 +53493,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5">
-    <cfRule type="containsText" dxfId="621" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="624" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53510,7 +53510,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="containsText" dxfId="620" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="623" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53527,7 +53527,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="containsText" dxfId="619" priority="199" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="622" priority="199" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53544,7 +53544,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5">
-    <cfRule type="containsText" dxfId="618" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="621" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53561,7 +53561,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="containsText" dxfId="617" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="620" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53578,7 +53578,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7">
-    <cfRule type="containsText" dxfId="616" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="619" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53595,7 +53595,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7">
-    <cfRule type="containsText" dxfId="615" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="618" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53636,17 +53636,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14">
-    <cfRule type="containsText" dxfId="614" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="617" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M14">
-    <cfRule type="containsText" dxfId="613" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="616" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11">
-    <cfRule type="containsText" dxfId="612" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="615" priority="179" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53663,7 +53663,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N14">
-    <cfRule type="containsText" dxfId="611" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="614" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53680,7 +53680,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13">
-    <cfRule type="containsText" dxfId="610" priority="177" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="613" priority="177" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53721,17 +53721,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L17">
-    <cfRule type="containsText" dxfId="609" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="612" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19">
-    <cfRule type="containsText" dxfId="608" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="611" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19">
-    <cfRule type="containsText" dxfId="607" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="610" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53772,17 +53772,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21">
-    <cfRule type="containsText" dxfId="606" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="609" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21">
-    <cfRule type="containsText" dxfId="605" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="608" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19">
-    <cfRule type="containsText" dxfId="604" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="607" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53799,7 +53799,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="containsText" dxfId="603" priority="141" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="606" priority="141" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53816,7 +53816,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21">
-    <cfRule type="containsText" dxfId="602" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="605" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53833,7 +53833,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="containsText" dxfId="601" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="604" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53862,12 +53862,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L35">
-    <cfRule type="containsText" dxfId="600" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="603" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="599" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="602" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53884,7 +53884,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="containsText" dxfId="598" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="601" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53913,12 +53913,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L28">
-    <cfRule type="containsText" dxfId="597" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="600" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M28">
-    <cfRule type="containsText" dxfId="596" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="599" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53935,7 +53935,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N28">
-    <cfRule type="containsText" dxfId="595" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="598" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53964,12 +53964,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L30">
-    <cfRule type="containsText" dxfId="594" priority="125" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="597" priority="125" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M30">
-    <cfRule type="containsText" dxfId="593" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="596" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53986,7 +53986,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N30">
-    <cfRule type="containsText" dxfId="592" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="595" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54003,7 +54003,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35">
-    <cfRule type="containsText" dxfId="591" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="594" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54020,7 +54020,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:N31">
-    <cfRule type="containsText" dxfId="590" priority="117" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="593" priority="117" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54037,7 +54037,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32">
-    <cfRule type="containsText" dxfId="589" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="592" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54054,7 +54054,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33">
-    <cfRule type="containsText" dxfId="588" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="591" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54071,7 +54071,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33">
-    <cfRule type="containsText" dxfId="587" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="590" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54088,7 +54088,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L34">
-    <cfRule type="containsText" dxfId="586" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="589" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54105,7 +54105,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M40:M41 M43 M51 M61:M63">
-    <cfRule type="containsText" dxfId="585" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="588" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54122,7 +54122,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M34:N34">
-    <cfRule type="containsText" dxfId="584" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="587" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54151,12 +54151,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40:L41 L43 L57:L58 L62">
-    <cfRule type="containsText" dxfId="583" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="586" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35">
-    <cfRule type="containsText" dxfId="582" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="585" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54173,7 +54173,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L36">
-    <cfRule type="containsText" dxfId="581" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="584" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54190,7 +54190,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N36">
-    <cfRule type="containsText" dxfId="580" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="583" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54207,7 +54207,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M36">
-    <cfRule type="containsText" dxfId="579" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="582" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54224,7 +54224,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="containsText" dxfId="578" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="581" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54241,7 +54241,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M38">
-    <cfRule type="containsText" dxfId="577" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="580" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54258,7 +54258,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N38">
-    <cfRule type="containsText" dxfId="576" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="579" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54275,7 +54275,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L39">
-    <cfRule type="containsText" dxfId="575" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="578" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54292,7 +54292,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N39">
-    <cfRule type="containsText" dxfId="574" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="577" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54309,7 +54309,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N40:N41 N43:N44 N57 N61:N63">
-    <cfRule type="containsText" dxfId="573" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="576" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54326,7 +54326,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M42">
-    <cfRule type="containsText" dxfId="572" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="575" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54343,7 +54343,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L42">
-    <cfRule type="containsText" dxfId="571" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="574" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54360,7 +54360,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N42">
-    <cfRule type="containsText" dxfId="570" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="573" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54377,7 +54377,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M45">
-    <cfRule type="containsText" dxfId="569" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="572" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54394,7 +54394,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="containsText" dxfId="568" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="571" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54411,7 +54411,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N45:N46">
-    <cfRule type="containsText" dxfId="567" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="570" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54428,7 +54428,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M48">
-    <cfRule type="containsText" dxfId="566" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="569" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54445,7 +54445,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L48">
-    <cfRule type="containsText" dxfId="565" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="568" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54462,7 +54462,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N48">
-    <cfRule type="containsText" dxfId="564" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="567" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54479,7 +54479,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M54">
-    <cfRule type="containsText" dxfId="563" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="566" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54496,7 +54496,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L54:L55">
-    <cfRule type="containsText" dxfId="562" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="565" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54513,7 +54513,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N54">
-    <cfRule type="containsText" dxfId="561" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="564" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54530,7 +54530,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L46">
-    <cfRule type="containsText" dxfId="560" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="563" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54547,7 +54547,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P46">
-    <cfRule type="containsText" dxfId="559" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="562" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54564,7 +54564,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N49">
-    <cfRule type="containsText" dxfId="558" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="561" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54581,7 +54581,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47">
-    <cfRule type="containsText" dxfId="557" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="560" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54598,7 +54598,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P50">
-    <cfRule type="containsText" dxfId="556" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="559" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54615,7 +54615,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O46">
-    <cfRule type="containsText" dxfId="555" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="558" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54632,7 +54632,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M46">
-    <cfRule type="containsText" dxfId="554" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="557" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54649,7 +54649,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N52">
-    <cfRule type="containsText" dxfId="553" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="556" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54666,7 +54666,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47">
-    <cfRule type="containsText" dxfId="552" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="555" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54683,7 +54683,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O53">
-    <cfRule type="containsText" dxfId="551" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="554" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54700,7 +54700,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O49">
-    <cfRule type="containsText" dxfId="550" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="553" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54717,7 +54717,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49">
-    <cfRule type="containsText" dxfId="549" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="552" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54734,7 +54734,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49">
-    <cfRule type="containsText" dxfId="548" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="551" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54751,7 +54751,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M52">
-    <cfRule type="containsText" dxfId="547" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="550" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54768,7 +54768,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P52">
-    <cfRule type="containsText" dxfId="546" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="549" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54785,7 +54785,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M56">
-    <cfRule type="containsText" dxfId="545" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="548" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54802,7 +54802,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52">
-    <cfRule type="containsText" dxfId="544" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="547" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54819,7 +54819,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N55">
-    <cfRule type="containsText" dxfId="543" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="546" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54836,7 +54836,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O55">
-    <cfRule type="containsText" dxfId="542" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="545" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54853,7 +54853,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O56">
-    <cfRule type="containsText" dxfId="541" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="544" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54870,7 +54870,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O61">
-    <cfRule type="containsText" dxfId="540" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="543" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57698,7 +57698,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J29 J33 J35">
+  <conditionalFormatting sqref="J33 J29 J35">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -57710,7 +57710,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K29 K33 K35">
+  <conditionalFormatting sqref="K33 K29 K35">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -57746,7 +57746,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I29 I33 I35 I39 I41 I43">
+  <conditionalFormatting sqref="I33 I29 I35 I39 I41 I43">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -57794,7 +57794,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K30 K32 K34 K36">
+  <conditionalFormatting sqref="K32 K30 K34 K36">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -57806,7 +57806,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I30 I32 I34 I36 I44">
+  <conditionalFormatting sqref="I32 I30 I34 I36 I44">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -57831,7 +57831,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J29 J33 J35">
-    <cfRule type="containsText" dxfId="539" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="542" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57848,47 +57848,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29 K33 K35">
-    <cfRule type="containsText" dxfId="538" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="541" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="537" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="540" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="536" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="539" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32">
-    <cfRule type="containsText" dxfId="535" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="538" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="534" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="537" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="533" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="536" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30 K32 K34 K36">
-    <cfRule type="containsText" dxfId="532" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="535" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="531" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="534" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="containsText" dxfId="530" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="533" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57905,7 +57905,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16">
-    <cfRule type="containsText" dxfId="529" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="532" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57922,7 +57922,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="528" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="531" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57939,12 +57939,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29 I33 I35 I39 I41 I43">
-    <cfRule type="containsText" dxfId="527" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="530" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30 I32 I34 I36 I44">
-    <cfRule type="containsText" dxfId="526" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="529" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57961,7 +57961,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="containsText" dxfId="525" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="528" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57978,12 +57978,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31">
-    <cfRule type="containsText" dxfId="524" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="527" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31">
-    <cfRule type="containsText" dxfId="523" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="526" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -58000,7 +58000,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="containsText" dxfId="522" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="525" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -58017,7 +58017,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I37">
-    <cfRule type="containsText" dxfId="521" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="524" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -58034,12 +58034,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="containsText" dxfId="520" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="523" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38">
-    <cfRule type="containsText" dxfId="519" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="522" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63239,7 +63239,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="M6 M8 M10">
+  <conditionalFormatting sqref="M8 M6 M10">
     <cfRule type="colorScale" priority="302">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -63251,7 +63251,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6 L8 L10 L18 L33 L39 L50 L55">
+  <conditionalFormatting sqref="L8 L6 L10 L18 L33 L39 L50 L55">
     <cfRule type="colorScale" priority="304">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -63299,7 +63299,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3 L5 L7 L9 L11">
+  <conditionalFormatting sqref="L5 L3 L7 L9 L11">
     <cfRule type="colorScale" priority="310">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -63312,11 +63312,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3 L5 L7 L9 L11">
-    <cfRule type="containsText" dxfId="518" priority="309" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="521" priority="309" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3 M5 M7 M9 M11">
+  <conditionalFormatting sqref="M5 M3 M7 M9 M11">
     <cfRule type="colorScale" priority="308">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -63329,12 +63329,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3 M5 M7 M9 M11">
-    <cfRule type="containsText" dxfId="517" priority="307" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="520" priority="307" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6 L8 L10 L18 L33 L39 L50 L55">
-    <cfRule type="containsText" dxfId="516" priority="303" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="519" priority="303" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63351,27 +63351,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6 M8 M10">
-    <cfRule type="containsText" dxfId="515" priority="301" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="518" priority="301" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L12">
-    <cfRule type="containsText" dxfId="514" priority="297" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="517" priority="297" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13">
-    <cfRule type="containsText" dxfId="513" priority="293" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="516" priority="293" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13">
-    <cfRule type="containsText" dxfId="512" priority="291" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="515" priority="291" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M14">
-    <cfRule type="containsText" dxfId="511" priority="285" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="514" priority="285" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63388,11 +63388,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12">
-    <cfRule type="containsText" dxfId="510" priority="273" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="513" priority="273" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K33 K39 K43 K49:K50 K55 K61 K68">
+  <conditionalFormatting sqref="K39 K33 K43 K49:K50 K55 K61 K68">
     <cfRule type="colorScale" priority="272">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -63405,7 +63405,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33 K39 K43 K49:K50 K55 K61 K68">
-    <cfRule type="containsText" dxfId="509" priority="271" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="512" priority="271" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63422,7 +63422,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19 M26:M29 M39 M43 M49:M50 M53 M55 M58 M61 M68">
-    <cfRule type="containsText" dxfId="508" priority="269" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="511" priority="269" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63439,7 +63439,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21">
-    <cfRule type="containsText" dxfId="507" priority="261" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="510" priority="261" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63456,7 +63456,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21">
-    <cfRule type="containsText" dxfId="506" priority="259" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="509" priority="259" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63473,7 +63473,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20">
-    <cfRule type="containsText" dxfId="505" priority="249" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="508" priority="249" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63490,7 +63490,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L22">
-    <cfRule type="containsText" dxfId="504" priority="247" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="507" priority="247" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63507,7 +63507,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L24">
-    <cfRule type="containsText" dxfId="503" priority="245" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="506" priority="245" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63524,7 +63524,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24">
-    <cfRule type="containsText" dxfId="502" priority="243" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="505" priority="243" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63541,7 +63541,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24">
-    <cfRule type="containsText" dxfId="501" priority="241" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="504" priority="241" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63558,7 +63558,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28">
-    <cfRule type="containsText" dxfId="500" priority="239" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="503" priority="239" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63575,7 +63575,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29">
-    <cfRule type="containsText" dxfId="499" priority="237" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="502" priority="237" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63592,7 +63592,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31">
-    <cfRule type="containsText" dxfId="498" priority="211" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="501" priority="211" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63609,7 +63609,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L32">
-    <cfRule type="containsText" dxfId="497" priority="229" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="500" priority="229" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63626,7 +63626,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="containsText" dxfId="496" priority="227" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="499" priority="227" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63643,7 +63643,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35">
-    <cfRule type="containsText" dxfId="495" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="498" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63660,7 +63660,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L37">
-    <cfRule type="containsText" dxfId="494" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="497" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63677,7 +63677,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="containsText" dxfId="493" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="496" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63694,7 +63694,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L36">
-    <cfRule type="containsText" dxfId="492" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="495" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63711,7 +63711,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36">
-    <cfRule type="containsText" dxfId="491" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="494" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63728,7 +63728,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40">
-    <cfRule type="containsText" dxfId="490" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="493" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63745,7 +63745,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L41">
-    <cfRule type="containsText" dxfId="489" priority="185" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="492" priority="185" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63762,7 +63762,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L44">
-    <cfRule type="containsText" dxfId="488" priority="183" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="491" priority="183" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63779,7 +63779,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="containsText" dxfId="487" priority="181" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="490" priority="181" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63796,7 +63796,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L47">
-    <cfRule type="containsText" dxfId="486" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="489" priority="179" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63813,7 +63813,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47">
-    <cfRule type="containsText" dxfId="485" priority="177" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="488" priority="177" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63830,7 +63830,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47">
-    <cfRule type="containsText" dxfId="484" priority="175" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="487" priority="175" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63847,7 +63847,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L51">
-    <cfRule type="containsText" dxfId="483" priority="173" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="486" priority="173" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63864,7 +63864,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52">
-    <cfRule type="containsText" dxfId="482" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="485" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63881,7 +63881,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M52">
-    <cfRule type="containsText" dxfId="481" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="484" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63898,7 +63898,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L54">
-    <cfRule type="containsText" dxfId="480" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="483" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63915,7 +63915,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K54">
-    <cfRule type="containsText" dxfId="479" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="482" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63932,7 +63932,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M54">
-    <cfRule type="containsText" dxfId="478" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="481" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63949,7 +63949,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O55">
-    <cfRule type="containsText" dxfId="477" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="480" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63966,7 +63966,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L56">
-    <cfRule type="containsText" dxfId="476" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="479" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63983,7 +63983,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K56">
-    <cfRule type="containsText" dxfId="475" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="478" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64000,7 +64000,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M56">
-    <cfRule type="containsText" dxfId="474" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="477" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64017,7 +64017,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L57">
-    <cfRule type="containsText" dxfId="473" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="476" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64034,7 +64034,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K57">
-    <cfRule type="containsText" dxfId="472" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="475" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64051,7 +64051,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M57">
-    <cfRule type="containsText" dxfId="471" priority="149" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="474" priority="149" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64068,7 +64068,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60">
-    <cfRule type="containsText" dxfId="470" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="473" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64085,7 +64085,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L58">
-    <cfRule type="containsText" dxfId="469" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="472" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64102,7 +64102,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58">
-    <cfRule type="containsText" dxfId="468" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="471" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64119,7 +64119,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L59">
-    <cfRule type="containsText" dxfId="467" priority="141" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="470" priority="141" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64136,7 +64136,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K64">
-    <cfRule type="containsText" dxfId="466" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="469" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64153,7 +64153,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59">
-    <cfRule type="containsText" dxfId="465" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="468" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64170,7 +64170,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L62">
-    <cfRule type="containsText" dxfId="464" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="467" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64187,7 +64187,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K62">
-    <cfRule type="containsText" dxfId="463" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="466" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64204,7 +64204,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M62">
-    <cfRule type="containsText" dxfId="462" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="465" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64221,7 +64221,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L64">
-    <cfRule type="containsText" dxfId="461" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="464" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64238,7 +64238,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64">
-    <cfRule type="containsText" dxfId="460" priority="125" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="463" priority="125" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64255,7 +64255,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L63">
-    <cfRule type="containsText" dxfId="459" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="462" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64272,7 +64272,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63">
-    <cfRule type="containsText" dxfId="458" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="461" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64289,7 +64289,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M63">
-    <cfRule type="containsText" dxfId="457" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="460" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64306,7 +64306,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N63:O63">
-    <cfRule type="containsText" dxfId="456" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="459" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64323,7 +64323,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N67">
-    <cfRule type="containsText" dxfId="455" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="458" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64340,7 +64340,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L66">
-    <cfRule type="containsText" dxfId="454" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="457" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64357,7 +64357,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L65">
-    <cfRule type="containsText" dxfId="453" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="456" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64374,7 +64374,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67">
-    <cfRule type="containsText" dxfId="452" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="455" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64391,7 +64391,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67">
-    <cfRule type="containsText" dxfId="451" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="454" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64408,7 +64408,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M79">
-    <cfRule type="containsText" dxfId="450" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="453" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64425,7 +64425,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N69">
-    <cfRule type="containsText" dxfId="449" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="452" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64442,7 +64442,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K69">
-    <cfRule type="containsText" dxfId="448" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="451" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64459,7 +64459,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L69">
-    <cfRule type="containsText" dxfId="447" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="450" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64476,7 +64476,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M69">
-    <cfRule type="containsText" dxfId="446" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="449" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64493,7 +64493,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80">
-    <cfRule type="containsText" dxfId="445" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="448" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64510,7 +64510,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L80">
-    <cfRule type="containsText" dxfId="444" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="447" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64527,7 +64527,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M80">
-    <cfRule type="containsText" dxfId="443" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="446" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64544,7 +64544,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K81">
-    <cfRule type="containsText" dxfId="442" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="445" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64561,7 +64561,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L81">
-    <cfRule type="containsText" dxfId="441" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="444" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64578,7 +64578,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M81">
-    <cfRule type="containsText" dxfId="440" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="443" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64595,7 +64595,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N70">
-    <cfRule type="containsText" dxfId="439" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="442" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64612,7 +64612,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K70">
-    <cfRule type="containsText" dxfId="438" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="441" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64629,7 +64629,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L70">
-    <cfRule type="containsText" dxfId="437" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="440" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64646,7 +64646,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M70">
-    <cfRule type="containsText" dxfId="436" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="439" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64663,7 +64663,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N71">
-    <cfRule type="containsText" dxfId="435" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="438" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64680,7 +64680,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K71">
-    <cfRule type="containsText" dxfId="434" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="437" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64697,7 +64697,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L71">
-    <cfRule type="containsText" dxfId="433" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="436" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64714,7 +64714,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M71">
-    <cfRule type="containsText" dxfId="432" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="435" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64731,7 +64731,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N72">
-    <cfRule type="containsText" dxfId="431" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="434" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64748,7 +64748,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K72">
-    <cfRule type="containsText" dxfId="430" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="433" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64765,7 +64765,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L72">
-    <cfRule type="containsText" dxfId="429" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="432" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64782,7 +64782,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M72">
-    <cfRule type="containsText" dxfId="428" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="431" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64799,7 +64799,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N73">
-    <cfRule type="containsText" dxfId="427" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="430" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64816,7 +64816,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K73">
-    <cfRule type="containsText" dxfId="426" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="429" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64833,7 +64833,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L73">
-    <cfRule type="containsText" dxfId="425" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="428" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64850,7 +64850,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M73">
-    <cfRule type="containsText" dxfId="424" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="427" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64867,7 +64867,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N74">
-    <cfRule type="containsText" dxfId="423" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="426" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64884,7 +64884,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K74">
-    <cfRule type="containsText" dxfId="422" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="425" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64901,7 +64901,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L74">
-    <cfRule type="containsText" dxfId="421" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="424" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64918,7 +64918,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M74">
-    <cfRule type="containsText" dxfId="420" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="423" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64935,7 +64935,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N75">
-    <cfRule type="containsText" dxfId="419" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="422" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64952,7 +64952,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K75">
-    <cfRule type="containsText" dxfId="418" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="421" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64969,7 +64969,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L75">
-    <cfRule type="containsText" dxfId="417" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="420" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64986,7 +64986,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M75">
-    <cfRule type="containsText" dxfId="416" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="419" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65003,7 +65003,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N76">
-    <cfRule type="containsText" dxfId="415" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="418" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65020,7 +65020,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76">
-    <cfRule type="containsText" dxfId="414" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="417" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65037,7 +65037,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L76">
-    <cfRule type="containsText" dxfId="413" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="416" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65054,7 +65054,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M76">
-    <cfRule type="containsText" dxfId="412" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="415" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65071,7 +65071,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N77">
-    <cfRule type="containsText" dxfId="411" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="414" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65088,7 +65088,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K77">
-    <cfRule type="containsText" dxfId="410" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="413" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65105,7 +65105,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L77">
-    <cfRule type="containsText" dxfId="409" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="412" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65122,7 +65122,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M77">
-    <cfRule type="containsText" dxfId="408" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="411" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65139,7 +65139,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N78">
-    <cfRule type="containsText" dxfId="407" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="410" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65156,7 +65156,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78">
-    <cfRule type="containsText" dxfId="406" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="409" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65173,7 +65173,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L78">
-    <cfRule type="containsText" dxfId="405" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="408" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65190,7 +65190,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M78">
-    <cfRule type="containsText" dxfId="404" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="407" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65207,7 +65207,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N79">
-    <cfRule type="containsText" dxfId="403" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="406" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65224,7 +65224,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="containsText" dxfId="402" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="405" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65241,7 +65241,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="containsText" dxfId="401" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="404" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69775,7 +69775,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="M3 M7 M9">
+  <conditionalFormatting sqref="M7 M3 M9">
     <cfRule type="colorScale" priority="170">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -69787,7 +69787,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N6 N8 N10">
+  <conditionalFormatting sqref="N8 N6 N10">
     <cfRule type="colorScale" priority="162">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -69799,7 +69799,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6 M8">
+  <conditionalFormatting sqref="M8 M6">
     <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -69871,7 +69871,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N7 N9">
+  <conditionalFormatting sqref="N9 N7">
     <cfRule type="colorScale" priority="168">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -69884,17 +69884,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3 M7 M9">
-    <cfRule type="containsText" dxfId="400" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="403" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7 N9">
-    <cfRule type="containsText" dxfId="399" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="402" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6 M8">
-    <cfRule type="containsText" dxfId="398" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="401" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69911,7 +69911,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6 N8 N10">
-    <cfRule type="containsText" dxfId="397" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="400" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69928,7 +69928,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M14">
-    <cfRule type="containsText" dxfId="396" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="399" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69945,32 +69945,32 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13">
-    <cfRule type="containsText" dxfId="395" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="398" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16">
-    <cfRule type="containsText" dxfId="394" priority="141" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="397" priority="141" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16">
-    <cfRule type="containsText" dxfId="393" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="396" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N14:N15">
-    <cfRule type="containsText" dxfId="392" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="395" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="containsText" dxfId="391" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="394" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M17">
-    <cfRule type="containsText" dxfId="390" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="393" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69987,7 +69987,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N17">
-    <cfRule type="containsText" dxfId="389" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="392" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70004,12 +70004,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5">
-    <cfRule type="containsText" dxfId="388" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="391" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18">
-    <cfRule type="containsText" dxfId="387" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="390" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70026,7 +70026,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20">
-    <cfRule type="containsText" dxfId="386" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="389" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70043,7 +70043,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22">
-    <cfRule type="containsText" dxfId="385" priority="125" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="388" priority="125" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70060,7 +70060,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22">
-    <cfRule type="containsText" dxfId="384" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="387" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70077,7 +70077,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="containsText" dxfId="383" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="386" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70094,7 +70094,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="containsText" dxfId="382" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="385" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70111,7 +70111,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="containsText" dxfId="381" priority="117" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="384" priority="117" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70128,7 +70128,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24">
-    <cfRule type="containsText" dxfId="380" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="383" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70145,7 +70145,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="containsText" dxfId="379" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="382" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70162,7 +70162,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="containsText" dxfId="378" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="381" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70179,7 +70179,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="377" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="380" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70196,7 +70196,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L28">
-    <cfRule type="containsText" dxfId="376" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="379" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70213,7 +70213,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N28">
-    <cfRule type="containsText" dxfId="375" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="378" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70230,7 +70230,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M28">
-    <cfRule type="containsText" dxfId="374" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="377" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70247,7 +70247,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L30">
-    <cfRule type="containsText" dxfId="373" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="376" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70264,7 +70264,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N30">
-    <cfRule type="containsText" dxfId="372" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="375" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70281,7 +70281,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M30">
-    <cfRule type="containsText" dxfId="371" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="374" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70298,7 +70298,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32">
-    <cfRule type="containsText" dxfId="370" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="373" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70315,17 +70315,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32">
-    <cfRule type="containsText" dxfId="369" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="372" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N39">
-    <cfRule type="containsText" dxfId="368" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="371" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N40 N42 N44:N45">
-    <cfRule type="containsText" dxfId="367" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="370" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70342,7 +70342,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35">
-    <cfRule type="containsText" dxfId="366" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="369" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70359,7 +70359,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35">
-    <cfRule type="containsText" dxfId="365" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="368" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70375,7 +70375,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N40 N42 N44:N45">
+  <conditionalFormatting sqref="N42 N40 N44:N45">
     <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -70388,7 +70388,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O41">
-    <cfRule type="containsText" dxfId="364" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="367" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70405,7 +70405,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40:M40 L44:M44 M48">
-    <cfRule type="containsText" dxfId="363" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="366" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70422,11 +70422,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N41 N43 N46">
-    <cfRule type="containsText" dxfId="362" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="365" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N41 N43 N46">
+  <conditionalFormatting sqref="N43 N41 N46">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -70439,7 +70439,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L41:M41 L43:M43 L46:M46">
-    <cfRule type="containsText" dxfId="361" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="364" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70456,7 +70456,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q45">
-    <cfRule type="containsText" dxfId="360" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="363" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70473,7 +70473,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M45">
-    <cfRule type="containsText" dxfId="359" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="362" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70490,7 +70490,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="containsText" dxfId="358" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="361" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70507,7 +70507,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P45">
-    <cfRule type="containsText" dxfId="357" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="360" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70524,7 +70524,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47">
-    <cfRule type="containsText" dxfId="356" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="359" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70541,7 +70541,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L47:M47">
-    <cfRule type="containsText" dxfId="355" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="358" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70558,7 +70558,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47">
-    <cfRule type="containsText" dxfId="354" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="357" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70575,11 +70575,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N49 N51 N53 N55 N57 N59 N61 N65">
-    <cfRule type="containsText" dxfId="353" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="356" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N49 N51 N53 N55 N57 N59 N61 N65">
+  <conditionalFormatting sqref="N51 N49 N53 N55 N57 N59 N61 N65">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -70592,7 +70592,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49:M49 L51:M51 L53:M53 L55:M55 L57:M57 L59:M59 L61:M61">
-    <cfRule type="containsText" dxfId="352" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="355" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70609,11 +70609,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P49 P51 P53 P55 P57 P59 P65">
-    <cfRule type="containsText" dxfId="351" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="354" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P49 P51 P53 P55 P57 P59 P65">
+  <conditionalFormatting sqref="P51 P49 P53 P55 P57 P59 P65">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -70626,11 +70626,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50 N52 N54 N56 N58 N60">
-    <cfRule type="containsText" dxfId="350" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="353" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N50 N52 N54 N56 N58 N60">
+  <conditionalFormatting sqref="N52 N50 N54 N56 N58 N60">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -70643,7 +70643,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L50:M50 L52:M52 L54:M54 L56:M56 L58:M58 L60:M60">
-    <cfRule type="containsText" dxfId="349" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="352" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70660,11 +70660,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P50 P52 P54 P56 P58 P60">
-    <cfRule type="containsText" dxfId="348" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="351" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P50 P52 P54 P56 P58 P60">
+  <conditionalFormatting sqref="P52 P50 P54 P56 P58 P60">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -70677,7 +70677,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61">
-    <cfRule type="containsText" dxfId="347" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="350" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70694,7 +70694,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N66">
-    <cfRule type="containsText" dxfId="346" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="349" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70711,7 +70711,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P66">
-    <cfRule type="containsText" dxfId="345" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="348" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70728,7 +70728,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M66">
-    <cfRule type="containsText" dxfId="344" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="347" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70745,7 +70745,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N74">
-    <cfRule type="containsText" dxfId="343" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="346" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70762,7 +70762,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N67">
-    <cfRule type="containsText" dxfId="342" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="345" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70779,7 +70779,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M69">
-    <cfRule type="containsText" dxfId="341" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="344" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70796,7 +70796,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M67">
-    <cfRule type="containsText" dxfId="340" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="343" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70813,7 +70813,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N71">
-    <cfRule type="containsText" dxfId="339" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="342" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70830,7 +70830,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N68">
-    <cfRule type="containsText" dxfId="338" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="341" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70847,7 +70847,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N73">
-    <cfRule type="containsText" dxfId="337" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="340" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70864,7 +70864,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N69">
-    <cfRule type="containsText" dxfId="336" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="339" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70881,7 +70881,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L69">
-    <cfRule type="containsText" dxfId="335" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="338" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -77507,7 +77507,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="4">
         <v>0</v>
@@ -78453,12 +78453,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8">
-    <cfRule type="containsText" dxfId="334" priority="263" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="337" priority="263" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q8">
-    <cfRule type="containsText" dxfId="333" priority="261" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="336" priority="261" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78487,7 +78487,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P16">
-    <cfRule type="containsText" dxfId="332" priority="233" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="335" priority="233" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78504,7 +78504,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P22">
-    <cfRule type="containsText" dxfId="331" priority="229" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="334" priority="229" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78521,7 +78521,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q22">
-    <cfRule type="containsText" dxfId="330" priority="227" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="333" priority="227" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78538,7 +78538,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q23">
-    <cfRule type="containsText" dxfId="329" priority="225" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="332" priority="225" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78555,7 +78555,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P24">
-    <cfRule type="containsText" dxfId="328" priority="223" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="331" priority="223" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78572,7 +78572,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26">
-    <cfRule type="containsText" dxfId="327" priority="221" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="330" priority="221" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78589,12 +78589,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q26">
-    <cfRule type="containsText" dxfId="326" priority="219" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="329" priority="219" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P28">
-    <cfRule type="containsText" dxfId="325" priority="217" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="328" priority="217" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78611,7 +78611,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P32">
-    <cfRule type="containsText" dxfId="324" priority="215" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="327" priority="215" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78628,7 +78628,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q32">
-    <cfRule type="containsText" dxfId="323" priority="213" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="326" priority="213" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78645,7 +78645,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P33">
-    <cfRule type="containsText" dxfId="322" priority="211" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="325" priority="211" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78662,7 +78662,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q33">
-    <cfRule type="containsText" dxfId="321" priority="209" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="324" priority="209" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78679,7 +78679,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P35">
-    <cfRule type="containsText" dxfId="320" priority="203" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="323" priority="203" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78696,7 +78696,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q35">
-    <cfRule type="containsText" dxfId="319" priority="201" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="322" priority="201" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78713,7 +78713,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="containsText" dxfId="318" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="321" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78730,7 +78730,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P39">
-    <cfRule type="containsText" dxfId="317" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="320" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78747,11 +78747,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37">
-    <cfRule type="containsText" dxfId="316" priority="199" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="319" priority="199" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P43 P41 P45">
+  <conditionalFormatting sqref="P41 P43 P45">
     <cfRule type="colorScale" priority="190">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -78764,11 +78764,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P41 P43 P45">
-    <cfRule type="containsText" dxfId="315" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="318" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q43 Q41 Q45">
+  <conditionalFormatting sqref="Q41 Q43 Q45">
     <cfRule type="colorScale" priority="188">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -78781,11 +78781,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q41 Q43 Q45">
-    <cfRule type="containsText" dxfId="314" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="317" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q40 Q44 Q49">
+  <conditionalFormatting sqref="Q44 Q40 Q49">
     <cfRule type="colorScale" priority="192">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -78798,11 +78798,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40 Q44 Q49">
-    <cfRule type="containsText" dxfId="313" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="316" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P40 P44">
+  <conditionalFormatting sqref="P44 P40">
     <cfRule type="colorScale" priority="194">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -78815,7 +78815,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P40 P44">
-    <cfRule type="containsText" dxfId="312" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="315" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78832,7 +78832,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O41">
-    <cfRule type="containsText" dxfId="311" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="314" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78849,7 +78849,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q42">
-    <cfRule type="containsText" dxfId="310" priority="177" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="313" priority="177" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78866,7 +78866,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S42">
-    <cfRule type="containsText" dxfId="309" priority="175" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="312" priority="175" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78883,7 +78883,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42">
-    <cfRule type="containsText" dxfId="308" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="311" priority="179" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78900,12 +78900,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T42">
-    <cfRule type="containsText" dxfId="307" priority="173" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="310" priority="173" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O44">
-    <cfRule type="containsText" dxfId="306" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="309" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78922,7 +78922,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O43">
-    <cfRule type="containsText" dxfId="305" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="308" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78951,7 +78951,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q46">
-    <cfRule type="containsText" dxfId="304" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="307" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78968,7 +78968,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O45">
-    <cfRule type="containsText" dxfId="303" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="306" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78985,7 +78985,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R45">
-    <cfRule type="containsText" dxfId="302" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="305" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79002,7 +79002,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47">
-    <cfRule type="containsText" dxfId="301" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="304" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79019,7 +79019,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P48">
-    <cfRule type="containsText" dxfId="300" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="303" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79036,7 +79036,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q50">
-    <cfRule type="containsText" dxfId="299" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="302" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79053,7 +79053,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O53">
-    <cfRule type="containsText" dxfId="298" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="301" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79070,7 +79070,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P52">
-    <cfRule type="containsText" dxfId="297" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="300" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79087,7 +79087,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P55">
-    <cfRule type="containsText" dxfId="296" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="299" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79104,7 +79104,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O54">
-    <cfRule type="containsText" dxfId="295" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="298" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79121,7 +79121,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O49">
-    <cfRule type="containsText" dxfId="294" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="297" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79138,7 +79138,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R56">
-    <cfRule type="containsText" dxfId="293" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="296" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79155,7 +79155,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P57">
-    <cfRule type="containsText" dxfId="292" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="295" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79172,7 +79172,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O50">
-    <cfRule type="containsText" dxfId="291" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="294" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79189,7 +79189,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P49:P50">
-    <cfRule type="containsText" dxfId="290" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="293" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79206,7 +79206,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R51">
-    <cfRule type="containsText" dxfId="289" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="292" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79223,7 +79223,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R58">
-    <cfRule type="containsText" dxfId="288" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="291" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79240,7 +79240,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q55">
-    <cfRule type="containsText" dxfId="287" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="290" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79257,7 +79257,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O58">
-    <cfRule type="containsText" dxfId="286" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="289" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79274,7 +79274,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P58">
-    <cfRule type="containsText" dxfId="285" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="288" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79291,7 +79291,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q58">
-    <cfRule type="containsText" dxfId="284" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="287" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79308,7 +79308,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q53">
-    <cfRule type="containsText" dxfId="283" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="286" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79325,7 +79325,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="containsText" dxfId="282" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="285" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79342,7 +79342,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O59">
-    <cfRule type="containsText" dxfId="281" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="284" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79359,7 +79359,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P59">
-    <cfRule type="containsText" dxfId="280" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="283" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79376,7 +79376,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O60">
-    <cfRule type="containsText" dxfId="279" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="282" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79393,7 +79393,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q60">
-    <cfRule type="containsText" dxfId="278" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="281" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79410,7 +79410,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R60">
-    <cfRule type="containsText" dxfId="277" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="280" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79427,7 +79427,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61">
-    <cfRule type="containsText" dxfId="276" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="279" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79444,7 +79444,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P62">
-    <cfRule type="containsText" dxfId="275" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="278" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79461,7 +79461,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P64">
-    <cfRule type="containsText" dxfId="274" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="277" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79478,7 +79478,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P65">
-    <cfRule type="containsText" dxfId="273" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="276" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79495,7 +79495,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O63">
-    <cfRule type="containsText" dxfId="272" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="275" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79512,7 +79512,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q63">
-    <cfRule type="containsText" dxfId="271" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="274" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79529,7 +79529,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R63">
-    <cfRule type="containsText" dxfId="270" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="273" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79546,7 +79546,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O66:R66 O67:P67 R67">
-    <cfRule type="containsText" dxfId="269" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="272" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79563,7 +79563,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O68">
-    <cfRule type="containsText" dxfId="268" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="271" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79580,7 +79580,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O69:R69">
-    <cfRule type="containsText" dxfId="267" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="270" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79597,7 +79597,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O70:R70">
-    <cfRule type="containsText" dxfId="266" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="269" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79614,7 +79614,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70">
-    <cfRule type="containsText" dxfId="265" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="268" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79631,7 +79631,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O71:R71">
-    <cfRule type="containsText" dxfId="264" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="267" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79648,7 +79648,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V72">
-    <cfRule type="containsText" dxfId="263" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="266" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79665,7 +79665,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U71">
-    <cfRule type="containsText" dxfId="262" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="265" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79682,7 +79682,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V73">
-    <cfRule type="containsText" dxfId="261" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="264" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79699,7 +79699,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V71">
-    <cfRule type="containsText" dxfId="260" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="263" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79716,7 +79716,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O72:R72">
-    <cfRule type="containsText" dxfId="259" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="262" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79733,7 +79733,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U72">
-    <cfRule type="containsText" dxfId="258" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="261" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79750,7 +79750,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O73:R73">
-    <cfRule type="containsText" dxfId="257" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="260" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79767,7 +79767,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U73">
-    <cfRule type="containsText" dxfId="256" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="259" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79784,7 +79784,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O75">
-    <cfRule type="containsText" dxfId="255" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="258" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79801,7 +79801,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O76">
-    <cfRule type="containsText" dxfId="254" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="257" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79818,7 +79818,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V74">
-    <cfRule type="containsText" dxfId="253" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="256" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79835,7 +79835,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P74:R74">
-    <cfRule type="containsText" dxfId="252" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="255" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79852,7 +79852,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O78:R78 P80 O82 R80 R82">
-    <cfRule type="containsText" dxfId="251" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="254" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79869,7 +79869,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O77:R77">
-    <cfRule type="containsText" dxfId="250" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="253" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79886,7 +79886,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O83:R83 O85:R85 O87 Q87:R87">
-    <cfRule type="containsText" dxfId="249" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="252" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79903,12 +79903,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O79:R79 O81:R81">
-    <cfRule type="containsText" dxfId="248" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="251" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O84:R84 O86:R86">
-    <cfRule type="containsText" dxfId="247" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="250" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79925,7 +79925,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O88:R88 O90:R90 O92:R92 O94:R94 O96:R96">
-    <cfRule type="containsText" dxfId="246" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="249" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -79942,7 +79942,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O89:R89 O91:R91 O93:R93 O95:R95">
-    <cfRule type="containsText" dxfId="245" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="248" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
